--- a/Locker/Keys Lock Tracker - 2026 1.xlsx
+++ b/Locker/Keys Lock Tracker - 2026 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cbre-my.sharepoint.com/personal/satyabrata_mohanty1_cbre_com/Documents/Desktop/Trackers/Locker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="223" documentId="11_F56D8C5A66DACF4247F893C0199D457268BC86FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9CB832C-57E5-4345-94F0-3676F07EA6C8}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="11_F56D8C5A66DACF4247F893C0199D457268BC86FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3371508D-8647-4A87-B65F-6FD419172296}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2339" uniqueCount="390">
   <si>
     <t>📊 Executive Dashboard</t>
   </si>
@@ -654,6 +654,9 @@
     <t>Box No-9</t>
   </si>
   <si>
+    <t>Box No-10</t>
+  </si>
+  <si>
     <t>Near MR - 501</t>
   </si>
   <si>
@@ -690,6 +693,9 @@
     <t>Near Workstation (613-634)</t>
   </si>
   <si>
+    <t>Box no-10</t>
+  </si>
+  <si>
     <t>Network &amp; Power Cables</t>
   </si>
   <si>
@@ -807,6 +813,9 @@
     <t>Pantry Fruits Storage</t>
   </si>
   <si>
+    <t>Box No-13</t>
+  </si>
+  <si>
     <t>Chai Point Vendor</t>
   </si>
   <si>
@@ -991,6 +1000,9 @@
   </si>
   <si>
     <t>Wellnees room</t>
+  </si>
+  <si>
+    <t>near MR 601</t>
   </si>
   <si>
     <t>⚠️ FACILITY ACTION ITEMS &amp; KEY AUDIT RESOLUTION TRACKER</t>
@@ -3042,14 +3054,14 @@
     <row r="12" spans="2:16" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="67">
         <f>SUM(Table_Tracker[Total Keys])</f>
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C12" s="43"/>
       <c r="D12" s="43"/>
       <c r="E12" s="15"/>
       <c r="F12" s="68">
         <f>SUM(Table_Tracker[Spare Keys (BMS)])</f>
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G12" s="43"/>
       <c r="H12" s="43"/>
@@ -3063,7 +3075,7 @@
       <c r="M12" s="15"/>
       <c r="N12" s="75">
         <f>SUM(Table_Tracker[Missing Keys])</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O12" s="43"/>
       <c r="P12" s="43"/>
@@ -3193,7 +3205,7 @@
       </c>
       <c r="K17" s="5">
         <f>COUNTIF(Table_Tracker[Lock Type], "Planter")</f>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L17" s="5">
         <f>COUNTIFS(Table_Tracker[Lock Type], "Planter", Table_Tracker[Lock Status], "Occupied")</f>
@@ -3205,7 +3217,7 @@
       </c>
       <c r="N17" s="5">
         <f>SUMIFS(Table_Tracker[Spare Keys (BMS)], Table_Tracker[Lock Type], "Planter")</f>
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O17" s="5">
         <f>SUMIFS(Table_Tracker[Issued Keys], Table_Tracker[Lock Type], "Planter")</f>
@@ -3213,7 +3225,7 @@
       </c>
       <c r="P17" s="5">
         <f>SUMIFS(Table_Tracker[Missing Keys], Table_Tracker[Lock Type], "Planter")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3393,11 +3405,11 @@
       </c>
       <c r="C21" s="18">
         <f>COUNTIF(Table_Tracker[Zone], B21)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D21" s="18">
         <f>COUNTIFS(Table_Tracker[Zone], B21, Table_Tracker[Lock Type], "Planter")</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
         <f>COUNTIFS(Table_Tracker[Zone], B21, Table_Tracker[Lock Type], "Cupboard")</f>
@@ -3478,7 +3490,7 @@
       </c>
       <c r="K22" s="7">
         <f t="shared" ref="K22:P22" si="0">SUM(K17:K21)</f>
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L22" s="7">
         <f t="shared" si="0"/>
@@ -3490,7 +3502,7 @@
       </c>
       <c r="N22" s="7">
         <f t="shared" si="0"/>
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O22" s="7">
         <f t="shared" si="0"/>
@@ -3498,7 +3510,7 @@
       </c>
       <c r="P22" s="7">
         <f t="shared" si="0"/>
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -3865,11 +3877,11 @@
       </c>
       <c r="C31" s="20">
         <f t="shared" ref="C31:H31" si="1">SUM(C17:C30)</f>
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D31" s="20">
         <f t="shared" si="1"/>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E31" s="20">
         <f t="shared" si="1"/>
@@ -8710,7 +8722,9 @@
       <c r="L87" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M87" s="28"/>
+      <c r="M87" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N87" s="14" t="s">
         <v>35</v>
       </c>
@@ -8736,7 +8750,7 @@
         <v>27</v>
       </c>
       <c r="E88" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F88" s="23">
         <v>2</v>
@@ -8761,7 +8775,9 @@
       <c r="L88" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M88" s="28"/>
+      <c r="M88" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N88" s="14" t="s">
         <v>34</v>
       </c>
@@ -8787,7 +8803,7 @@
         <v>27</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F89" s="23">
         <v>2</v>
@@ -8812,7 +8828,9 @@
       <c r="L89" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M89" s="28"/>
+      <c r="M89" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N89" s="14" t="s">
         <v>34</v>
       </c>
@@ -8838,7 +8856,7 @@
         <v>27</v>
       </c>
       <c r="E90" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F90" s="23">
         <v>2</v>
@@ -8863,7 +8881,9 @@
       <c r="L90" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M90" s="28"/>
+      <c r="M90" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N90" s="14" t="s">
         <v>34</v>
       </c>
@@ -8889,7 +8909,7 @@
         <v>27</v>
       </c>
       <c r="E91" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F91" s="23">
         <v>2</v>
@@ -8914,7 +8934,9 @@
       <c r="L91" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M91" s="28"/>
+      <c r="M91" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N91" s="14" t="s">
         <v>34</v>
       </c>
@@ -8940,7 +8962,7 @@
         <v>27</v>
       </c>
       <c r="E92" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F92" s="23">
         <v>2</v>
@@ -8965,7 +8987,9 @@
       <c r="L92" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M92" s="28"/>
+      <c r="M92" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N92" s="14" t="s">
         <v>34</v>
       </c>
@@ -8991,7 +9015,7 @@
         <v>27</v>
       </c>
       <c r="E93" s="23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F93" s="23">
         <v>2</v>
@@ -9016,7 +9040,9 @@
       <c r="L93" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M93" s="28"/>
+      <c r="M93" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N93" s="14" t="s">
         <v>35</v>
       </c>
@@ -9042,7 +9068,7 @@
         <v>27</v>
       </c>
       <c r="E94" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F94" s="23">
         <v>2</v>
@@ -9062,7 +9088,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K94" s="23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L94" s="23" t="s">
         <v>137</v>
@@ -9072,7 +9098,7 @@
         <v>34</v>
       </c>
       <c r="O94" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P94" s="14" t="str">
         <f t="shared" si="5"/>
@@ -9093,7 +9119,7 @@
         <v>27</v>
       </c>
       <c r="E95" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F95" s="23">
         <v>2</v>
@@ -9144,7 +9170,7 @@
         <v>27</v>
       </c>
       <c r="E96" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F96" s="23">
         <v>2</v>
@@ -9169,7 +9195,9 @@
       <c r="L96" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M96" s="28"/>
+      <c r="M96" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N96" s="14" t="s">
         <v>35</v>
       </c>
@@ -9195,7 +9223,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F97" s="23">
         <v>2</v>
@@ -9215,12 +9243,14 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K97" s="23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L97" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M97" s="28"/>
+      <c r="M97" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N97" s="14" t="s">
         <v>34</v>
       </c>
@@ -9246,7 +9276,7 @@
         <v>27</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F98" s="23">
         <v>2</v>
@@ -9271,7 +9301,9 @@
       <c r="L98" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M98" s="28"/>
+      <c r="M98" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N98" s="14" t="s">
         <v>34</v>
       </c>
@@ -9297,7 +9329,7 @@
         <v>27</v>
       </c>
       <c r="E99" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F99" s="23">
         <v>2</v>
@@ -9322,7 +9354,9 @@
       <c r="L99" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M99" s="28"/>
+      <c r="M99" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N99" s="14" t="s">
         <v>34</v>
       </c>
@@ -9348,7 +9382,7 @@
         <v>27</v>
       </c>
       <c r="E100" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F100" s="23">
         <v>2</v>
@@ -9373,7 +9407,9 @@
       <c r="L100" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M100" s="28"/>
+      <c r="M100" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N100" s="14" t="s">
         <v>34</v>
       </c>
@@ -9399,7 +9435,7 @@
         <v>27</v>
       </c>
       <c r="E101" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F101" s="23">
         <v>2</v>
@@ -9429,7 +9465,7 @@
         <v>34</v>
       </c>
       <c r="O101" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P101" s="14" t="str">
         <f t="shared" si="5"/>
@@ -9450,7 +9486,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F102" s="23">
         <v>2</v>
@@ -9475,7 +9511,9 @@
       <c r="L102" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M102" s="28"/>
+      <c r="M102" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N102" s="14" t="s">
         <v>35</v>
       </c>
@@ -9501,7 +9539,7 @@
         <v>27</v>
       </c>
       <c r="E103" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F103" s="23">
         <v>2</v>
@@ -9531,7 +9569,7 @@
         <v>34</v>
       </c>
       <c r="O103" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P103" s="14" t="str">
         <f t="shared" si="5"/>
@@ -9552,7 +9590,7 @@
         <v>27</v>
       </c>
       <c r="E104" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F104" s="23">
         <v>2</v>
@@ -9582,7 +9620,7 @@
         <v>34</v>
       </c>
       <c r="O104" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P104" s="14" t="str">
         <f t="shared" si="5"/>
@@ -9628,7 +9666,9 @@
       <c r="L105" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M105" s="28"/>
+      <c r="M105" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N105" s="14" t="s">
         <v>34</v>
       </c>
@@ -9674,17 +9714,19 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K106" s="23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L106" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M106" s="28"/>
+      <c r="M106" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N106" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O106" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P106" s="14" t="str">
         <f t="shared" si="5"/>
@@ -9705,7 +9747,7 @@
         <v>27</v>
       </c>
       <c r="E107" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F107" s="23">
         <v>2</v>
@@ -9730,12 +9772,14 @@
       <c r="L107" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M107" s="28"/>
+      <c r="M107" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N107" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O107" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P107" s="14" t="str">
         <f t="shared" si="5"/>
@@ -9756,7 +9800,7 @@
         <v>27</v>
       </c>
       <c r="E108" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F108" s="23">
         <v>2</v>
@@ -9781,7 +9825,9 @@
       <c r="L108" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M108" s="28"/>
+      <c r="M108" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N108" s="14" t="s">
         <v>34</v>
       </c>
@@ -9807,7 +9853,7 @@
         <v>27</v>
       </c>
       <c r="E109" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F109" s="23">
         <v>2</v>
@@ -9832,7 +9878,9 @@
       <c r="L109" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M109" s="28"/>
+      <c r="M109" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N109" s="14" t="s">
         <v>34</v>
       </c>
@@ -9858,7 +9906,7 @@
         <v>27</v>
       </c>
       <c r="E110" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F110" s="23">
         <v>2</v>
@@ -9883,7 +9931,9 @@
       <c r="L110" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M110" s="28"/>
+      <c r="M110" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N110" s="14" t="s">
         <v>34</v>
       </c>
@@ -9909,7 +9959,7 @@
         <v>27</v>
       </c>
       <c r="E111" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F111" s="23">
         <v>2</v>
@@ -9934,7 +9984,9 @@
       <c r="L111" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M111" s="28"/>
+      <c r="M111" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N111" s="14" t="s">
         <v>34</v>
       </c>
@@ -9960,7 +10012,7 @@
         <v>27</v>
       </c>
       <c r="E112" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F112" s="23">
         <v>2</v>
@@ -9985,12 +10037,14 @@
       <c r="L112" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M112" s="28"/>
+      <c r="M112" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N112" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O112" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P112" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10011,7 +10065,7 @@
         <v>27</v>
       </c>
       <c r="E113" s="23" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F113" s="23">
         <v>2</v>
@@ -10036,12 +10090,14 @@
       <c r="L113" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M113" s="28"/>
+      <c r="M113" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N113" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O113" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P113" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10062,7 +10118,7 @@
         <v>27</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F114" s="23">
         <v>2</v>
@@ -10092,7 +10148,7 @@
         <v>34</v>
       </c>
       <c r="O114" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P114" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10113,7 +10169,7 @@
         <v>27</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F115" s="23">
         <v>2</v>
@@ -10138,12 +10194,14 @@
       <c r="L115" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M115" s="28"/>
+      <c r="M115" s="28" t="s">
+        <v>217</v>
+      </c>
       <c r="N115" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O115" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P115" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10164,7 +10222,7 @@
         <v>27</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F116" s="23">
         <v>2</v>
@@ -10189,12 +10247,14 @@
       <c r="L116" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M116" s="28"/>
+      <c r="M116" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N116" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O116" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P116" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10215,7 +10275,7 @@
         <v>27</v>
       </c>
       <c r="E117" s="23" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F117" s="23">
         <v>2</v>
@@ -10240,12 +10300,14 @@
       <c r="L117" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M117" s="28"/>
+      <c r="M117" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N117" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O117" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P117" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10266,7 +10328,7 @@
         <v>27</v>
       </c>
       <c r="E118" s="23" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F118" s="23">
         <v>2</v>
@@ -10291,12 +10353,14 @@
       <c r="L118" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M118" s="28"/>
+      <c r="M118" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N118" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O118" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P118" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10347,7 +10411,7 @@
         <v>34</v>
       </c>
       <c r="O119" s="14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P119" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10502,7 +10566,7 @@
         <v>34</v>
       </c>
       <c r="O122" s="14" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P122" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10555,7 +10619,7 @@
         <v>34</v>
       </c>
       <c r="O123" s="14" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P123" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10606,7 +10670,7 @@
         <v>34</v>
       </c>
       <c r="O124" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P124" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10657,7 +10721,7 @@
         <v>34</v>
       </c>
       <c r="O125" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P125" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10708,7 +10772,7 @@
         <v>34</v>
       </c>
       <c r="O126" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P126" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10759,7 +10823,7 @@
         <v>34</v>
       </c>
       <c r="O127" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P127" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10810,7 +10874,7 @@
         <v>34</v>
       </c>
       <c r="O128" s="14" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P128" s="14" t="str">
         <f t="shared" si="5"/>
@@ -10882,7 +10946,7 @@
         <v>27</v>
       </c>
       <c r="E130" s="23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F130" s="23">
         <v>2</v>
@@ -10933,7 +10997,7 @@
         <v>27</v>
       </c>
       <c r="E131" s="23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F131" s="23">
         <v>2</v>
@@ -10959,7 +11023,7 @@
         <v>137</v>
       </c>
       <c r="M131" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N131" s="14" t="s">
         <v>34</v>
@@ -10986,7 +11050,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F132" s="23">
         <v>2</v>
@@ -11012,7 +11076,7 @@
         <v>137</v>
       </c>
       <c r="M132" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N132" s="14" t="s">
         <v>34</v>
@@ -11039,7 +11103,7 @@
         <v>27</v>
       </c>
       <c r="E133" s="23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F133" s="23">
         <v>2</v>
@@ -11065,7 +11129,7 @@
         <v>137</v>
       </c>
       <c r="M133" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N133" s="14" t="s">
         <v>34</v>
@@ -11092,7 +11156,7 @@
         <v>27</v>
       </c>
       <c r="E134" s="23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F134" s="23">
         <v>2</v>
@@ -11118,13 +11182,13 @@
         <v>137</v>
       </c>
       <c r="M134" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N134" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O134" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P134" s="14" t="str">
         <f t="shared" si="5"/>
@@ -11145,7 +11209,7 @@
         <v>27</v>
       </c>
       <c r="E135" s="23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F135" s="23">
         <v>2</v>
@@ -11171,13 +11235,13 @@
         <v>137</v>
       </c>
       <c r="M135" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N135" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O135" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P135" s="14" t="str">
         <f t="shared" si="5"/>
@@ -11198,7 +11262,7 @@
         <v>27</v>
       </c>
       <c r="E136" s="23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F136" s="23">
         <v>2</v>
@@ -11228,7 +11292,7 @@
         <v>34</v>
       </c>
       <c r="O136" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P136" s="14" t="str">
         <f t="shared" ref="P136:P200" si="8">IF(I136&gt;0, "🚨 REPLACE LOCK / KEY LOST", IF(ISNUMBER(SEARCH("Audit", O136)), "⚠️ AUDIT WITH EMPLOYEE", IF(ISNUMBER(SEARCH("Damaged", O136)), "⚠️ KEY DAMAGED / REPLACE", IF(ISNUMBER(SEARCH("Verification", O136)), "🔍 KEY VERIFICATION", IF(N136="Vacant", "🟢 AVAILABLE", "✅ OK")))))</f>
@@ -11249,7 +11313,7 @@
         <v>27</v>
       </c>
       <c r="E137" s="23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F137" s="23">
         <v>2</v>
@@ -11275,13 +11339,13 @@
         <v>137</v>
       </c>
       <c r="M137" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N137" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O137" s="14" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P137" s="14" t="str">
         <f t="shared" si="8"/>
@@ -11302,7 +11366,7 @@
         <v>27</v>
       </c>
       <c r="E138" s="23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F138" s="23">
         <v>2</v>
@@ -11328,13 +11392,13 @@
         <v>137</v>
       </c>
       <c r="M138" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N138" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O138" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P138" s="14" t="str">
         <f t="shared" si="8"/>
@@ -11348,14 +11412,14 @@
       <c r="B139" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C139" s="26">
+      <c r="C139" s="24">
         <v>1838</v>
       </c>
       <c r="D139" s="23" t="s">
         <v>27</v>
       </c>
       <c r="E139" s="23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F139" s="23">
         <v>2</v>
@@ -11375,17 +11439,19 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K139" s="23" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L139" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M139" s="28"/>
+      <c r="M139" s="28" t="s">
+        <v>223</v>
+      </c>
       <c r="N139" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O139" s="14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P139" s="14" t="str">
         <f t="shared" si="8"/>
@@ -11406,7 +11472,7 @@
         <v>27</v>
       </c>
       <c r="E140" s="23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F140" s="23">
         <v>2</v>
@@ -11457,7 +11523,7 @@
         <v>27</v>
       </c>
       <c r="E141" s="23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F141" s="23">
         <v>2</v>
@@ -11508,7 +11574,7 @@
         <v>27</v>
       </c>
       <c r="E142" s="23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F142" s="23">
         <v>2</v>
@@ -11559,7 +11625,7 @@
         <v>27</v>
       </c>
       <c r="E143" s="23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F143" s="23">
         <v>2</v>
@@ -11579,7 +11645,7 @@
         <v>🔒 In Custody</v>
       </c>
       <c r="K143" s="23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L143" s="23" t="s">
         <v>137</v>
@@ -11610,7 +11676,7 @@
         <v>27</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F144" s="23">
         <v>2</v>
@@ -11661,7 +11727,7 @@
         <v>27</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F145" s="23">
         <v>2</v>
@@ -11712,7 +11778,7 @@
         <v>27</v>
       </c>
       <c r="E146" s="23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F146" s="23">
         <v>2</v>
@@ -11738,7 +11804,7 @@
         <v>137</v>
       </c>
       <c r="M146" s="28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N146" s="14" t="s">
         <v>34</v>
@@ -11765,7 +11831,7 @@
         <v>27</v>
       </c>
       <c r="E147" s="23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F147" s="23">
         <v>2</v>
@@ -11816,7 +11882,7 @@
         <v>28</v>
       </c>
       <c r="E148" s="23" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F148" s="23">
         <v>2</v>
@@ -11836,17 +11902,17 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K148" s="23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L148" s="23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M148" s="28"/>
       <c r="N148" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O148" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P148" s="14" t="str">
         <f t="shared" si="8"/>
@@ -11899,7 +11965,7 @@
         <v>34</v>
       </c>
       <c r="O149" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P149" s="14" t="str">
         <f t="shared" si="8"/>
@@ -11952,7 +12018,7 @@
         <v>34</v>
       </c>
       <c r="O150" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P150" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12005,7 +12071,7 @@
         <v>34</v>
       </c>
       <c r="O151" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P151" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12058,7 +12124,7 @@
         <v>34</v>
       </c>
       <c r="O152" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P152" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12105,13 +12171,13 @@
         <v>137</v>
       </c>
       <c r="M153" s="28" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N153" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O153" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P153" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12164,7 +12230,7 @@
         <v>34</v>
       </c>
       <c r="O154" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P154" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12217,7 +12283,7 @@
         <v>34</v>
       </c>
       <c r="O155" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P155" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12270,7 +12336,7 @@
         <v>34</v>
       </c>
       <c r="O156" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P156" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12323,7 +12389,7 @@
         <v>34</v>
       </c>
       <c r="O157" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P157" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12364,7 +12430,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K158" s="23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L158" s="23" t="s">
         <v>63</v>
@@ -12374,7 +12440,7 @@
         <v>34</v>
       </c>
       <c r="O158" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P158" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12415,7 +12481,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K159" s="23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L159" s="23" t="s">
         <v>63</v>
@@ -12425,7 +12491,7 @@
         <v>34</v>
       </c>
       <c r="O159" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P159" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12476,7 +12542,7 @@
         <v>34</v>
       </c>
       <c r="O160" s="14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P160" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12527,7 +12593,7 @@
         <v>34</v>
       </c>
       <c r="O161" s="14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P161" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12578,7 +12644,7 @@
         <v>34</v>
       </c>
       <c r="O162" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P162" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12680,7 +12746,7 @@
         <v>34</v>
       </c>
       <c r="O164" s="14" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P164" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12772,7 +12838,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K166" s="23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L166" s="23" t="s">
         <v>63</v>
@@ -12782,7 +12848,7 @@
         <v>34</v>
       </c>
       <c r="O166" s="14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P166" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12823,7 +12889,7 @@
         <v>⚠️ Missing Key</v>
       </c>
       <c r="K167" s="23" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="L167" s="23" t="s">
         <v>63</v>
@@ -12833,7 +12899,7 @@
         <v>34</v>
       </c>
       <c r="O167" s="14" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P167" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12925,7 +12991,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K169" s="23" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L169" s="23" t="s">
         <v>63</v>
@@ -12935,7 +13001,7 @@
         <v>34</v>
       </c>
       <c r="O169" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P169" s="14" t="str">
         <f t="shared" si="8"/>
@@ -12976,7 +13042,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K170" s="23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L170" s="23" t="s">
         <v>63</v>
@@ -13027,7 +13093,7 @@
         <v>⚠️ Missing Key</v>
       </c>
       <c r="K171" s="23" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L171" s="23" t="s">
         <v>63</v>
@@ -13078,7 +13144,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K172" s="23" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L172" s="23" t="s">
         <v>63</v>
@@ -13129,7 +13195,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K173" s="23" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L173" s="23" t="s">
         <v>63</v>
@@ -13188,7 +13254,7 @@
         <v>34</v>
       </c>
       <c r="O174" s="14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P174" s="14" t="str">
         <f t="shared" si="8"/>
@@ -13229,7 +13295,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K175" s="23" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L175" s="23" t="s">
         <v>63</v>
@@ -13290,7 +13356,7 @@
         <v>34</v>
       </c>
       <c r="O176" s="14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P176" s="14" t="str">
         <f t="shared" si="8"/>
@@ -13341,7 +13407,7 @@
         <v>34</v>
       </c>
       <c r="O177" s="14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P177" s="14" t="str">
         <f t="shared" si="8"/>
@@ -13392,7 +13458,7 @@
         <v>34</v>
       </c>
       <c r="O178" s="14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P178" s="14" t="str">
         <f t="shared" si="8"/>
@@ -13428,7 +13494,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="23" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K179" s="23" t="s">
         <v>64</v>
@@ -13437,16 +13503,16 @@
         <v>137</v>
       </c>
       <c r="M179" s="28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N179" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O179" s="14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P179" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="180" spans="1:16" x14ac:dyDescent="0.35">
@@ -13463,7 +13529,7 @@
         <v>30</v>
       </c>
       <c r="E180" s="23" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F180" s="23">
         <v>2</v>
@@ -13493,7 +13559,7 @@
         <v>34</v>
       </c>
       <c r="O180" s="14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P180" s="14" t="str">
         <f t="shared" si="8"/>
@@ -13514,7 +13580,7 @@
         <v>30</v>
       </c>
       <c r="E181" s="23" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F181" s="23">
         <v>2</v>
@@ -13544,7 +13610,7 @@
         <v>34</v>
       </c>
       <c r="O181" s="14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P181" s="14" t="str">
         <f t="shared" si="8"/>
@@ -13565,7 +13631,7 @@
         <v>30</v>
       </c>
       <c r="E182" s="23" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F182" s="23">
         <v>2</v>
@@ -13590,12 +13656,14 @@
       <c r="L182" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M182" s="28"/>
+      <c r="M182" s="28" t="s">
+        <v>257</v>
+      </c>
       <c r="N182" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O182" s="14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P182" s="14" t="str">
         <f t="shared" si="8"/>
@@ -13616,7 +13684,7 @@
         <v>30</v>
       </c>
       <c r="E183" s="23" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F183" s="23">
         <v>2</v>
@@ -13641,12 +13709,14 @@
       <c r="L183" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M183" s="28"/>
+      <c r="M183" s="28" t="s">
+        <v>257</v>
+      </c>
       <c r="N183" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O183" s="14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P183" s="14" t="str">
         <f t="shared" si="8"/>
@@ -13667,7 +13737,7 @@
         <v>30</v>
       </c>
       <c r="E184" s="23" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F184" s="23">
         <v>2</v>
@@ -13687,17 +13757,19 @@
         <v>⚠️ Missing Key</v>
       </c>
       <c r="K184" s="23" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L184" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M184" s="28"/>
+      <c r="M184" s="28" t="s">
+        <v>257</v>
+      </c>
       <c r="N184" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O184" s="14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="P184" s="14" t="str">
         <f t="shared" si="8"/>
@@ -13718,7 +13790,7 @@
         <v>31</v>
       </c>
       <c r="E185" s="23" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F185" s="23">
         <v>3</v>
@@ -13741,11 +13813,11 @@
         <v>139</v>
       </c>
       <c r="L185" s="23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M185" s="28"/>
       <c r="N185" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O185" s="14" t="s">
         <v>139</v>
@@ -13769,7 +13841,7 @@
         <v>31</v>
       </c>
       <c r="E186" s="23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F186" s="23">
         <v>3</v>
@@ -13792,11 +13864,11 @@
         <v>139</v>
       </c>
       <c r="L186" s="23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M186" s="28"/>
       <c r="N186" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O186" s="14" t="s">
         <v>139</v>
@@ -13820,7 +13892,7 @@
         <v>31</v>
       </c>
       <c r="E187" s="23" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F187" s="23">
         <v>3</v>
@@ -13843,11 +13915,11 @@
         <v>139</v>
       </c>
       <c r="L187" s="23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M187" s="28"/>
       <c r="N187" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O187" s="14" t="s">
         <v>139</v>
@@ -13871,7 +13943,7 @@
         <v>31</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F188" s="23">
         <v>3</v>
@@ -13898,7 +13970,7 @@
       </c>
       <c r="M188" s="28"/>
       <c r="N188" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O188" s="14" t="s">
         <v>139</v>
@@ -13922,7 +13994,7 @@
         <v>31</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F189" s="23">
         <v>3</v>
@@ -13949,7 +14021,7 @@
       </c>
       <c r="M189" s="28"/>
       <c r="N189" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O189" s="14" t="s">
         <v>139</v>
@@ -13973,7 +14045,7 @@
         <v>31</v>
       </c>
       <c r="E190" s="23" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F190" s="23">
         <v>3</v>
@@ -14000,7 +14072,7 @@
       </c>
       <c r="M190" s="28"/>
       <c r="N190" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O190" s="14" t="s">
         <v>139</v>
@@ -14024,7 +14096,7 @@
         <v>31</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F191" s="23">
         <v>3</v>
@@ -14051,7 +14123,7 @@
       </c>
       <c r="M191" s="28"/>
       <c r="N191" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O191" s="14" t="s">
         <v>139</v>
@@ -14075,7 +14147,7 @@
         <v>31</v>
       </c>
       <c r="E192" s="23" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F192" s="23">
         <v>3</v>
@@ -14102,7 +14174,7 @@
       </c>
       <c r="M192" s="28"/>
       <c r="N192" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O192" s="14" t="s">
         <v>139</v>
@@ -14126,7 +14198,7 @@
         <v>31</v>
       </c>
       <c r="E193" s="23" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F193" s="23">
         <v>3</v>
@@ -14153,7 +14225,7 @@
       </c>
       <c r="M193" s="28"/>
       <c r="N193" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O193" s="14" t="s">
         <v>139</v>
@@ -14177,7 +14249,7 @@
         <v>31</v>
       </c>
       <c r="E194" s="23" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F194" s="23">
         <v>3</v>
@@ -14204,7 +14276,7 @@
       </c>
       <c r="M194" s="28"/>
       <c r="N194" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O194" s="14" t="s">
         <v>139</v>
@@ -14228,7 +14300,7 @@
         <v>31</v>
       </c>
       <c r="E195" s="23" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="F195" s="23">
         <v>3</v>
@@ -14255,7 +14327,7 @@
       </c>
       <c r="M195" s="28"/>
       <c r="N195" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O195" s="14" t="s">
         <v>139</v>
@@ -14279,7 +14351,7 @@
         <v>31</v>
       </c>
       <c r="E196" s="23" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F196" s="23">
         <v>3</v>
@@ -14306,7 +14378,7 @@
       </c>
       <c r="M196" s="28"/>
       <c r="N196" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O196" s="14" t="s">
         <v>139</v>
@@ -14330,7 +14402,7 @@
         <v>31</v>
       </c>
       <c r="E197" s="23" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F197" s="23">
         <v>3</v>
@@ -14357,7 +14429,7 @@
       </c>
       <c r="M197" s="28"/>
       <c r="N197" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O197" s="14" t="s">
         <v>139</v>
@@ -14381,7 +14453,7 @@
         <v>31</v>
       </c>
       <c r="E198" s="23" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F198" s="23">
         <v>3</v>
@@ -14408,7 +14480,7 @@
       </c>
       <c r="M198" s="28"/>
       <c r="N198" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O198" s="14" t="s">
         <v>139</v>
@@ -14432,7 +14504,7 @@
         <v>31</v>
       </c>
       <c r="E199" s="23" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="F199" s="23">
         <v>3</v>
@@ -14459,7 +14531,7 @@
       </c>
       <c r="M199" s="28"/>
       <c r="N199" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O199" s="14" t="s">
         <v>139</v>
@@ -14483,7 +14555,7 @@
         <v>31</v>
       </c>
       <c r="E200" s="23" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F200" s="23">
         <v>2</v>
@@ -14510,7 +14582,7 @@
       </c>
       <c r="M200" s="28"/>
       <c r="N200" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O200" s="14" t="s">
         <v>139</v>
@@ -14534,7 +14606,7 @@
         <v>31</v>
       </c>
       <c r="E201" s="23" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F201" s="23">
         <v>3</v>
@@ -14546,7 +14618,7 @@
         <v>0</v>
       </c>
       <c r="I201" s="23">
-        <f t="shared" ref="I201:I247" si="9">MAX(0, F201-G201-H201)</f>
+        <f t="shared" ref="I201:I251" si="9">MAX(0, F201-G201-H201)</f>
         <v>1</v>
       </c>
       <c r="J201" s="23" t="str">
@@ -14561,7 +14633,7 @@
       </c>
       <c r="M201" s="28"/>
       <c r="N201" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O201" s="14" t="s">
         <v>139</v>
@@ -14585,7 +14657,7 @@
         <v>31</v>
       </c>
       <c r="E202" s="23" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F202" s="23">
         <v>3</v>
@@ -14612,7 +14684,7 @@
       </c>
       <c r="M202" s="28"/>
       <c r="N202" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O202" s="14" t="s">
         <v>139</v>
@@ -14636,7 +14708,7 @@
         <v>31</v>
       </c>
       <c r="E203" s="23" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F203" s="23">
         <v>3</v>
@@ -14663,7 +14735,7 @@
       </c>
       <c r="M203" s="28"/>
       <c r="N203" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O203" s="14" t="s">
         <v>139</v>
@@ -14687,7 +14759,7 @@
         <v>31</v>
       </c>
       <c r="E204" s="23" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F204" s="23">
         <v>3</v>
@@ -14714,7 +14786,7 @@
       </c>
       <c r="M204" s="28"/>
       <c r="N204" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O204" s="14" t="s">
         <v>139</v>
@@ -14738,7 +14810,7 @@
         <v>31</v>
       </c>
       <c r="E205" s="23" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F205" s="23">
         <v>3</v>
@@ -14765,7 +14837,7 @@
       </c>
       <c r="M205" s="28"/>
       <c r="N205" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O205" s="14" t="s">
         <v>139</v>
@@ -14789,7 +14861,7 @@
         <v>31</v>
       </c>
       <c r="E206" s="23" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F206" s="23">
         <v>3</v>
@@ -14816,7 +14888,7 @@
       </c>
       <c r="M206" s="28"/>
       <c r="N206" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O206" s="14" t="s">
         <v>139</v>
@@ -14840,7 +14912,7 @@
         <v>31</v>
       </c>
       <c r="E207" s="23" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F207" s="23">
         <v>3</v>
@@ -14867,7 +14939,7 @@
       </c>
       <c r="M207" s="28"/>
       <c r="N207" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O207" s="14" t="s">
         <v>139</v>
@@ -14891,7 +14963,7 @@
         <v>31</v>
       </c>
       <c r="E208" s="23" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F208" s="23">
         <v>3</v>
@@ -14918,7 +14990,7 @@
       </c>
       <c r="M208" s="28"/>
       <c r="N208" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O208" s="14" t="s">
         <v>139</v>
@@ -14942,7 +15014,7 @@
         <v>31</v>
       </c>
       <c r="E209" s="23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F209" s="23">
         <v>3</v>
@@ -14969,7 +15041,7 @@
       </c>
       <c r="M209" s="28"/>
       <c r="N209" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O209" s="14" t="s">
         <v>139</v>
@@ -14993,7 +15065,7 @@
         <v>31</v>
       </c>
       <c r="E210" s="23" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F210" s="23">
         <v>3</v>
@@ -15020,7 +15092,7 @@
       </c>
       <c r="M210" s="28"/>
       <c r="N210" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O210" s="14" t="s">
         <v>139</v>
@@ -15044,7 +15116,7 @@
         <v>31</v>
       </c>
       <c r="E211" s="23" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F211" s="23">
         <v>3</v>
@@ -15071,7 +15143,7 @@
       </c>
       <c r="M211" s="28"/>
       <c r="N211" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O211" s="14" t="s">
         <v>139</v>
@@ -15095,7 +15167,7 @@
         <v>31</v>
       </c>
       <c r="E212" s="23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F212" s="23">
         <v>2</v>
@@ -15122,7 +15194,7 @@
       </c>
       <c r="M212" s="28"/>
       <c r="N212" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O212" s="14" t="s">
         <v>139</v>
@@ -15197,7 +15269,7 @@
         <v>28</v>
       </c>
       <c r="E214" s="23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F214" s="23">
         <v>2</v>
@@ -15217,7 +15289,7 @@
         <v>⚠️ Missing Key</v>
       </c>
       <c r="K214" s="23" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L214" s="23" t="s">
         <v>137</v>
@@ -15227,7 +15299,7 @@
         <v>34</v>
       </c>
       <c r="O214" s="14" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P214" s="14" t="str">
         <f t="shared" si="11"/>
@@ -15274,10 +15346,10 @@
         <v>137</v>
       </c>
       <c r="M215" s="28" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="N215" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O215" s="14" t="s">
         <v>139</v>
@@ -15378,7 +15450,7 @@
         <v>137</v>
       </c>
       <c r="M217" s="28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N217" s="14" t="s">
         <v>35</v>
@@ -15431,7 +15503,7 @@
         <v>137</v>
       </c>
       <c r="M218" s="28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N218" s="14" t="s">
         <v>34</v>
@@ -15458,7 +15530,7 @@
         <v>28</v>
       </c>
       <c r="E219" s="23" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F219" s="23">
         <v>2</v>
@@ -15485,7 +15557,7 @@
       </c>
       <c r="M219" s="28"/>
       <c r="N219" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O219" s="14" t="s">
         <v>139</v>
@@ -15509,7 +15581,7 @@
         <v>31</v>
       </c>
       <c r="E220" s="23" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F220" s="23">
         <v>2</v>
@@ -15536,7 +15608,7 @@
       </c>
       <c r="M220" s="28"/>
       <c r="N220" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O220" s="14" t="s">
         <v>188</v>
@@ -15560,7 +15632,7 @@
         <v>31</v>
       </c>
       <c r="E221" s="23" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F221" s="23">
         <v>2</v>
@@ -15587,7 +15659,7 @@
       </c>
       <c r="M221" s="28"/>
       <c r="N221" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O221" s="14" t="s">
         <v>188</v>
@@ -15611,7 +15683,7 @@
         <v>31</v>
       </c>
       <c r="E222" s="23" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F222" s="23">
         <v>2</v>
@@ -15638,7 +15710,7 @@
       </c>
       <c r="M222" s="28"/>
       <c r="N222" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O222" s="14" t="s">
         <v>188</v>
@@ -15662,7 +15734,7 @@
         <v>31</v>
       </c>
       <c r="E223" s="23" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F223" s="23">
         <v>2</v>
@@ -15689,7 +15761,7 @@
       </c>
       <c r="M223" s="28"/>
       <c r="N223" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O223" s="14" t="s">
         <v>188</v>
@@ -15713,7 +15785,7 @@
         <v>31</v>
       </c>
       <c r="E224" s="23" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F224" s="23">
         <v>2</v>
@@ -15740,7 +15812,7 @@
       </c>
       <c r="M224" s="28"/>
       <c r="N224" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O224" s="14" t="s">
         <v>139</v>
@@ -15764,7 +15836,7 @@
         <v>31</v>
       </c>
       <c r="E225" s="23" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F225" s="23">
         <v>2</v>
@@ -15791,7 +15863,7 @@
       </c>
       <c r="M225" s="28"/>
       <c r="N225" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O225" s="14" t="s">
         <v>139</v>
@@ -15815,7 +15887,7 @@
         <v>31</v>
       </c>
       <c r="E226" s="23" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F226" s="23">
         <v>3</v>
@@ -15842,7 +15914,7 @@
       </c>
       <c r="M226" s="28"/>
       <c r="N226" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O226" s="14" t="s">
         <v>139</v>
@@ -15866,7 +15938,7 @@
         <v>31</v>
       </c>
       <c r="E227" s="23" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F227" s="23">
         <v>3</v>
@@ -15895,7 +15967,7 @@
         <v>177</v>
       </c>
       <c r="N227" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O227" s="14" t="s">
         <v>139</v>
@@ -15919,7 +15991,7 @@
         <v>31</v>
       </c>
       <c r="E228" s="23" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="F228" s="23">
         <v>2</v>
@@ -15948,7 +16020,7 @@
         <v>177</v>
       </c>
       <c r="N228" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O228" s="14" t="s">
         <v>139</v>
@@ -15972,7 +16044,7 @@
         <v>31</v>
       </c>
       <c r="E229" s="23" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F229" s="23">
         <v>3</v>
@@ -15999,7 +16071,7 @@
       </c>
       <c r="M229" s="28"/>
       <c r="N229" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O229" s="14" t="s">
         <v>139</v>
@@ -16023,7 +16095,7 @@
         <v>31</v>
       </c>
       <c r="E230" s="23" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F230" s="23">
         <v>3</v>
@@ -16050,7 +16122,7 @@
       </c>
       <c r="M230" s="28"/>
       <c r="N230" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O230" s="14" t="s">
         <v>139</v>
@@ -16074,7 +16146,7 @@
         <v>31</v>
       </c>
       <c r="E231" s="23" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="F231" s="23">
         <v>3</v>
@@ -16097,11 +16169,11 @@
         <v>139</v>
       </c>
       <c r="L231" s="23" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M231" s="28"/>
       <c r="N231" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O231" s="14" t="s">
         <v>139</v>
@@ -16125,7 +16197,7 @@
         <v>31</v>
       </c>
       <c r="E232" s="23" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F232" s="23">
         <v>3</v>
@@ -16152,7 +16224,7 @@
       </c>
       <c r="M232" s="28"/>
       <c r="N232" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O232" s="14" t="s">
         <v>139</v>
@@ -16176,7 +16248,7 @@
         <v>31</v>
       </c>
       <c r="E233" s="23" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F233" s="23">
         <v>2</v>
@@ -16203,7 +16275,7 @@
       </c>
       <c r="M233" s="28"/>
       <c r="N233" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O233" s="14" t="s">
         <v>139</v>
@@ -16227,7 +16299,7 @@
         <v>31</v>
       </c>
       <c r="E234" s="23" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F234" s="23">
         <v>3</v>
@@ -16254,7 +16326,7 @@
       </c>
       <c r="M234" s="28"/>
       <c r="N234" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O234" s="14" t="s">
         <v>139</v>
@@ -16278,7 +16350,7 @@
         <v>31</v>
       </c>
       <c r="E235" s="23" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F235" s="23">
         <v>2</v>
@@ -16305,7 +16377,7 @@
       </c>
       <c r="M235" s="28"/>
       <c r="N235" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O235" s="14" t="s">
         <v>139</v>
@@ -16329,7 +16401,7 @@
         <v>31</v>
       </c>
       <c r="E236" s="23" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F236" s="23">
         <v>2</v>
@@ -16356,7 +16428,7 @@
       </c>
       <c r="M236" s="28"/>
       <c r="N236" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O236" s="14" t="s">
         <v>139</v>
@@ -16380,7 +16452,7 @@
         <v>31</v>
       </c>
       <c r="E237" s="23" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="F237" s="23">
         <v>9</v>
@@ -16407,7 +16479,7 @@
       </c>
       <c r="M237" s="28"/>
       <c r="N237" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O237" s="14" t="s">
         <v>139</v>
@@ -16431,7 +16503,7 @@
         <v>31</v>
       </c>
       <c r="E238" s="23" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F238" s="23">
         <v>4</v>
@@ -16458,7 +16530,7 @@
       </c>
       <c r="M238" s="28"/>
       <c r="N238" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O238" s="14" t="s">
         <v>139</v>
@@ -16482,7 +16554,7 @@
         <v>28</v>
       </c>
       <c r="E239" s="23" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F239" s="23">
         <v>2</v>
@@ -16505,14 +16577,14 @@
         <v>70</v>
       </c>
       <c r="L239" s="23" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M239" s="28"/>
       <c r="N239" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O239" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P239" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16533,7 +16605,7 @@
         <v>28</v>
       </c>
       <c r="E240" s="23" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F240" s="23">
         <v>2</v>
@@ -16556,14 +16628,14 @@
         <v>70</v>
       </c>
       <c r="L240" s="23" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M240" s="28"/>
       <c r="N240" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O240" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P240" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16584,7 +16656,7 @@
         <v>28</v>
       </c>
       <c r="E241" s="23" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F241" s="23">
         <v>2</v>
@@ -16607,14 +16679,14 @@
         <v>70</v>
       </c>
       <c r="L241" s="23" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M241" s="28"/>
       <c r="N241" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O241" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P241" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16635,7 +16707,7 @@
         <v>28</v>
       </c>
       <c r="E242" s="23" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F242" s="23">
         <v>2</v>
@@ -16658,14 +16730,14 @@
         <v>70</v>
       </c>
       <c r="L242" s="23" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M242" s="28"/>
       <c r="N242" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O242" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P242" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16686,7 +16758,7 @@
         <v>28</v>
       </c>
       <c r="E243" s="23" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F243" s="23">
         <v>2</v>
@@ -16709,14 +16781,14 @@
         <v>70</v>
       </c>
       <c r="L243" s="23" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M243" s="28"/>
       <c r="N243" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O243" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P243" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16737,7 +16809,7 @@
         <v>28</v>
       </c>
       <c r="E244" s="23" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F244" s="23">
         <v>2</v>
@@ -16760,14 +16832,14 @@
         <v>70</v>
       </c>
       <c r="L244" s="23" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="M244" s="28"/>
       <c r="N244" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O244" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P244" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16817,10 +16889,10 @@
         <v>195</v>
       </c>
       <c r="N245" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O245" s="14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="P245" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16870,10 +16942,10 @@
         <v>192</v>
       </c>
       <c r="N246" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O246" s="14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="P246" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16919,12 +16991,14 @@
       <c r="L247" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M247" s="28"/>
+      <c r="M247" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N247" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O247" s="14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="P247" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16945,7 +17019,7 @@
         <v>28</v>
       </c>
       <c r="E248" s="23" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F248" s="23">
         <v>2</v>
@@ -16957,6 +17031,7 @@
         <v>0</v>
       </c>
       <c r="I248" s="23">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J248" s="23" t="str">
@@ -16970,13 +17045,13 @@
         <v>137</v>
       </c>
       <c r="M248" s="28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N248" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O248" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P248" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16997,7 +17072,7 @@
         <v>28</v>
       </c>
       <c r="E249" s="23" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F249" s="23">
         <v>2</v>
@@ -17009,6 +17084,7 @@
         <v>0</v>
       </c>
       <c r="I249" s="23">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J249" s="23" t="str">
@@ -17022,13 +17098,13 @@
         <v>137</v>
       </c>
       <c r="M249" s="28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="N249" s="14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O249" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P249" s="14" t="str">
         <f t="shared" si="11"/>
@@ -17050,7 +17126,10 @@
       <c r="F250" s="23"/>
       <c r="G250" s="23"/>
       <c r="H250" s="23"/>
-      <c r="I250" s="23"/>
+      <c r="I250" s="23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="J250" s="23" t="str">
         <f t="shared" si="10"/>
         <v>⚪ Unregistered</v>
@@ -17069,28 +17148,47 @@
       <c r="A251" s="23">
         <v>244</v>
       </c>
-      <c r="B251" s="23"/>
+      <c r="B251" s="23" t="s">
+        <v>47</v>
+      </c>
       <c r="C251" s="24">
-        <v>6444</v>
-      </c>
-      <c r="D251" s="23"/>
-      <c r="E251" s="23"/>
-      <c r="F251" s="23"/>
-      <c r="G251" s="23"/>
-      <c r="H251" s="23"/>
-      <c r="I251" s="23"/>
+        <v>7520</v>
+      </c>
+      <c r="D251" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E251" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="F251" s="23">
+        <v>2</v>
+      </c>
+      <c r="G251" s="23">
+        <v>1</v>
+      </c>
+      <c r="H251" s="23">
+        <v>0</v>
+      </c>
+      <c r="I251" s="23">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
       <c r="J251" s="23" t="str">
         <f t="shared" si="10"/>
-        <v>⚪ Unregistered</v>
+        <v>⚠️ Missing Key</v>
       </c>
       <c r="K251" s="23"/>
-      <c r="L251" s="23"/>
-      <c r="M251" s="28"/>
+      <c r="L251" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="M251" s="28" t="s">
+        <v>204</v>
+      </c>
       <c r="N251" s="14"/>
       <c r="O251" s="14"/>
       <c r="P251" s="14" t="str">
         <f t="shared" si="11"/>
-        <v>✅ OK</v>
+        <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.35">
@@ -17525,7 +17623,7 @@
     </row>
     <row r="4" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="69" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B4" s="43"/>
       <c r="C4" s="43"/>
@@ -17541,7 +17639,7 @@
     </row>
     <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="66" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
@@ -17572,13 +17670,13 @@
         <v>124</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>88</v>
@@ -17587,10 +17685,10 @@
         <v>89</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
@@ -17613,10 +17711,10 @@
         <v>188</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I8" s="23" t="s">
         <v>108</v>
@@ -17625,10 +17723,10 @@
         <v>109</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
@@ -17651,10 +17749,10 @@
         <v>188</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I9" s="23" t="s">
         <v>108</v>
@@ -17663,10 +17761,10 @@
         <v>109</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
@@ -17689,10 +17787,10 @@
         <v>188</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I10" s="23" t="s">
         <v>108</v>
@@ -17701,10 +17799,10 @@
         <v>109</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
@@ -17727,10 +17825,10 @@
         <v>198</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I11" s="23" t="s">
         <v>94</v>
@@ -17739,10 +17837,10 @@
         <v>95</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -17765,10 +17863,10 @@
         <v>188</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>108</v>
@@ -17777,10 +17875,10 @@
         <v>109</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
@@ -17803,10 +17901,10 @@
         <v>201</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I13" s="23" t="s">
         <v>108</v>
@@ -17815,10 +17913,10 @@
         <v>109</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
@@ -17841,10 +17939,10 @@
         <v>188</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I14" s="23" t="s">
         <v>108</v>
@@ -17853,15 +17951,15 @@
         <v>109</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="23" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>49</v>
@@ -17873,16 +17971,16 @@
         <v>27</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F15" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I15" s="23" t="s">
         <v>108</v>
@@ -17891,15 +17989,15 @@
         <v>109</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="23" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>49</v>
@@ -17911,16 +18009,16 @@
         <v>27</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F16" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I16" s="23" t="s">
         <v>108</v>
@@ -17929,15 +18027,15 @@
         <v>109</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="23" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>59</v>
@@ -17952,13 +18050,13 @@
         <v>59</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I17" s="23" t="s">
         <v>108</v>
@@ -17967,15 +18065,15 @@
         <v>109</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="23" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="B18" s="23" t="s">
         <v>63</v>
@@ -17990,13 +18088,13 @@
         <v>63</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I18" s="23" t="s">
         <v>108</v>
@@ -18005,15 +18103,15 @@
         <v>109</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="23" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B19" s="23" t="s">
         <v>63</v>
@@ -18028,13 +18126,13 @@
         <v>63</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I19" s="23" t="s">
         <v>108</v>
@@ -18043,15 +18141,15 @@
         <v>109</v>
       </c>
       <c r="K19" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="23" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>43</v>
@@ -18066,13 +18164,13 @@
         <v>103</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I20" s="23" t="s">
         <v>94</v>
@@ -18081,15 +18179,15 @@
         <v>95</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="23" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>54</v>
@@ -18101,16 +18199,16 @@
         <v>31</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I21" s="23" t="s">
         <v>108</v>
@@ -18119,15 +18217,15 @@
         <v>109</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="23" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>45</v>
@@ -18139,16 +18237,16 @@
         <v>31</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F22" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I22" s="23" t="s">
         <v>108</v>
@@ -18157,15 +18255,15 @@
         <v>109</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="23" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B23" s="23" t="s">
         <v>54</v>
@@ -18177,16 +18275,16 @@
         <v>31</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I23" s="23" t="s">
         <v>108</v>
@@ -18195,15 +18293,15 @@
         <v>109</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="23" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B24" s="23" t="s">
         <v>54</v>
@@ -18215,16 +18313,16 @@
         <v>31</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F24" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="I24" s="23" t="s">
         <v>108</v>
@@ -18233,15 +18331,15 @@
         <v>109</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="23" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B25" s="23" t="s">
         <v>45</v>
@@ -18256,13 +18354,13 @@
         <v>92</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I25" s="23" t="s">
         <v>94</v>
@@ -18271,15 +18369,15 @@
         <v>95</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="23" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>45</v>
@@ -18294,13 +18392,13 @@
         <v>92</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I26" s="23" t="s">
         <v>94</v>
@@ -18309,15 +18407,15 @@
         <v>95</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="23" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>47</v>
@@ -18332,13 +18430,13 @@
         <v>100</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="I27" s="23" t="s">
         <v>94</v>
@@ -18347,10 +18445,10 @@
         <v>95</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -18434,7 +18532,7 @@
     </row>
     <row r="4" spans="2:14" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="69" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C4" s="43"/>
       <c r="D4" s="43"/>
@@ -18451,7 +18549,7 @@
     </row>
     <row r="5" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="66" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C5" s="43"/>
       <c r="D5" s="43"/>
@@ -18468,7 +18566,7 @@
     </row>
     <row r="7" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="46" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C7" s="47"/>
       <c r="D7" s="47"/>
@@ -18485,25 +18583,25 @@
     </row>
     <row r="8" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="16" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>34</v>
@@ -18512,10 +18610,10 @@
         <v>35</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>127</v>
@@ -18742,11 +18840,11 @@
       </c>
       <c r="C13" s="18">
         <f>COUNTIF(Table_Tracker[Zone], B13)</f>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="18">
         <f>COUNTIFS(Table_Tracker[Zone], B13, Table_Tracker[Lock Type], "Planter")</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13" s="18">
         <f>COUNTIFS(Table_Tracker[Zone], B13, Table_Tracker[Lock Type], "Cupboard")</f>
@@ -18778,7 +18876,7 @@
       </c>
       <c r="L13" s="18">
         <f>SUMIFS(Table_Tracker[Spare Keys (BMS)], Table_Tracker[Zone], B13)</f>
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M13" s="18">
         <f>SUMIFS(Table_Tracker[Issued Keys], Table_Tracker[Zone], B13)</f>
@@ -18786,7 +18884,7 @@
       </c>
       <c r="N13" s="18">
         <f>SUMIFS(Table_Tracker[Missing Keys], Table_Tracker[Zone], B13)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -19268,15 +19366,15 @@
     </row>
     <row r="23" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="19" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C23" s="20">
         <f t="shared" ref="C23:N23" si="0">SUM(C9:C22)</f>
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D23" s="20">
         <f t="shared" si="0"/>
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E23" s="20">
         <f t="shared" si="0"/>
@@ -19308,7 +19406,7 @@
       </c>
       <c r="L23" s="20">
         <f t="shared" si="0"/>
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M23" s="20">
         <f t="shared" si="0"/>
@@ -19316,7 +19414,7 @@
       </c>
       <c r="N23" s="20">
         <f t="shared" si="0"/>
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -19382,7 +19480,7 @@
     </row>
     <row r="4" spans="1:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="69" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B4" s="43"/>
       <c r="C4" s="43"/>
@@ -19397,27 +19495,27 @@
     </row>
     <row r="5" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="3" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -19442,7 +19540,7 @@
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -19467,7 +19565,7 @@
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -19480,19 +19578,19 @@
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="4" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="4" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="4" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -19505,7 +19603,7 @@
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F9" s="15"/>
       <c r="G9" s="4" t="s">
@@ -19526,7 +19624,7 @@
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>

--- a/Locker/Keys Lock Tracker - 2026 1.xlsx
+++ b/Locker/Keys Lock Tracker - 2026 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cbre-my.sharepoint.com/personal/satyabrata_mohanty1_cbre_com/Documents/Desktop/Trackers/Locker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="317" documentId="11_F56D8C5A66DACF4247F893C0199D457268BC86FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3371508D-8647-4A87-B65F-6FD419172296}"/>
+  <xr:revisionPtr revIDLastSave="342" documentId="11_F56D8C5A66DACF4247F893C0199D457268BC86FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0669E165-B7FC-433A-91B0-D711E43EEF81}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2339" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="392">
   <si>
     <t>📊 Executive Dashboard</t>
   </si>
@@ -750,6 +750,9 @@
     <t>box no. 2</t>
   </si>
   <si>
+    <t>Box No-14</t>
+  </si>
+  <si>
     <t>Action: Key Verification Required</t>
   </si>
   <si>
@@ -781,6 +784,9 @@
   </si>
   <si>
     <t>Maya Negi</t>
+  </si>
+  <si>
+    <t>Box NO-14</t>
   </si>
   <si>
     <t>Plumbing Tools &amp; Spares</t>
@@ -1216,7 +1222,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2000,14 +2006,66 @@
     <xf numFmtId="0" fontId="24" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="16" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="7" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2017,8 +2075,6 @@
     <xf numFmtId="0" fontId="14" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2026,9 +2082,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2040,219 +2093,19 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="14" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="16" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF166534"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF991B1B"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF991B1B"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF166534"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDCFCE7"/>
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF3C7"/>
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF991B1B"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE2E2"/>
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF92400E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF3C7"/>
-          <bgColor rgb="FFFEF3C7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF166534"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDCFCE7"/>
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF1E40AF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDBEAFE"/>
-          <bgColor rgb="FFDBEAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color rgb="FF991B1B"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEE2E2"/>
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF78350F"/>
-        <name val="Segoe UI"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEF08A"/>
-          <bgColor rgb="FFFEF08A"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center"/>
       <border>
@@ -2517,7 +2370,160 @@
     <dxf>
       <font>
         <b/>
+        <color rgb="FF166534"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCFCE7"/>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF92400E"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF3C7"/>
+          <bgColor rgb="FFFEF3C7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF166534"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCFCE7"/>
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF1E40AF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBEAFE"/>
+          <bgColor rgb="FFDBEAFE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF991B1B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEE2E2"/>
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF78350F"/>
+        <name val="Segoe UI"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEF08A"/>
+          <bgColor rgb="FFFEF08A"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2534,7 +2540,14 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_Tracker" displayName="Table_Tracker" ref="A7:P257">
-  <autoFilter ref="A7:P257" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+  <autoFilter ref="A7:P257" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="705"/>
+        <filter val="(NonBlanks)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="S.No."/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Zone"/>
@@ -2548,7 +2561,7 @@
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Key Status"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Key Issued To"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Custodian Location"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Spare Key Location (Box Name)" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Spare Key Location (Box Name)" dataDxfId="18"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Lock Status"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Remarks &amp; Material"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Action Flag"/>
@@ -2558,21 +2571,21 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_ActionAudit" displayName="Table_ActionAudit" ref="A7:L27" totalsRowShown="0" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_ActionAudit" displayName="Table_ActionAudit" ref="A7:L27" totalsRowShown="0" dataDxfId="12">
   <autoFilter ref="A7:L27" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Action ID" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Zone" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lock No." dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Lock Type" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Location" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Current Issue / Gap" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Required Operational Action" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Responsible Team" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Priority" dataDxfId="16"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Target Date" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Resolution Status" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Audit Reference" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Action ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Zone" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lock No." dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Lock Type" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Location" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Current Issue / Gap" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Required Operational Action" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Responsible Team" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Priority" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Target Date" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Resolution Status" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Audit Reference" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2869,20 +2882,20 @@
     <tabColor rgb="FF1B365D"/>
   </sheetPr>
   <dimension ref="B2:P42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="3.7265625" customWidth="1"/>
-    <col min="2" max="2" width="22.7265625" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" customWidth="1"/>
-    <col min="4" max="8" width="10.7265625" customWidth="1"/>
-    <col min="9" max="9" width="4.7265625" customWidth="1"/>
-    <col min="10" max="10" width="20.7265625" customWidth="1"/>
-    <col min="11" max="15" width="12.7265625" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" customWidth="1"/>
-    <col min="17" max="17" width="3.7265625" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="11" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" ht="27.95" customHeight="1">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2909,224 +2922,224 @@
       </c>
       <c r="P2" s="15"/>
     </row>
-    <row r="4" spans="2:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="69" t="s">
+    <row r="4" spans="2:16" ht="24.95" customHeight="1">
+      <c r="B4" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-    </row>
-    <row r="5" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="66" t="s">
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+    </row>
+    <row r="5" spans="2:16" ht="18" customHeight="1">
+      <c r="B5" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="43"/>
-    </row>
-    <row r="7" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="71" t="s">
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+    </row>
+    <row r="7" spans="2:16" ht="18" customHeight="1">
+      <c r="B7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
       <c r="E7" s="15"/>
-      <c r="F7" s="76" t="s">
+      <c r="F7" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
       <c r="I7" s="15"/>
-      <c r="J7" s="56" t="s">
+      <c r="J7" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
       <c r="M7" s="15"/>
-      <c r="N7" s="73" t="s">
+      <c r="N7" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-    </row>
-    <row r="8" spans="2:16" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="51">
+      <c r="O7" s="69"/>
+      <c r="P7" s="69"/>
+    </row>
+    <row r="8" spans="2:16" ht="27.95" customHeight="1">
+      <c r="B8" s="65">
         <f>COUNTA(Table_Tracker[Lock No.])</f>
         <v>244</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="42">
+      <c r="F8" s="59">
         <f>COUNTIF(Table_Tracker[Lock Status], "Occupied")</f>
         <v>160</v>
       </c>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
       <c r="I8" s="15"/>
-      <c r="J8" s="68">
+      <c r="J8" s="50">
         <f>COUNTIF(Table_Tracker[Lock Status], "Vacant")</f>
         <v>21</v>
       </c>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
       <c r="M8" s="15"/>
-      <c r="N8" s="45">
+      <c r="N8" s="61">
         <f>COUNTIF(Table_Tracker[Lock Status], "Common Asset")</f>
         <v>54</v>
       </c>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-    </row>
-    <row r="9" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="54" t="s">
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
+    </row>
+    <row r="9" spans="2:16" ht="15.95" customHeight="1">
+      <c r="B9" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
       <c r="E9" s="15"/>
-      <c r="F9" s="55" t="s">
+      <c r="F9" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="52" t="s">
+      <c r="J9" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="69"/>
       <c r="M9" s="15"/>
-      <c r="N9" s="49" t="s">
+      <c r="N9" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-    </row>
-    <row r="11" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="50" t="s">
+      <c r="O9" s="69"/>
+      <c r="P9" s="69"/>
+    </row>
+    <row r="11" spans="2:16" ht="18" customHeight="1">
+      <c r="B11" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
       <c r="E11" s="15"/>
-      <c r="F11" s="56" t="s">
+      <c r="F11" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
       <c r="I11" s="15"/>
-      <c r="J11" s="58" t="s">
+      <c r="J11" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43"/>
+      <c r="K11" s="69"/>
+      <c r="L11" s="69"/>
       <c r="M11" s="15"/>
-      <c r="N11" s="72" t="s">
+      <c r="N11" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-    </row>
-    <row r="12" spans="2:16" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="67">
+      <c r="O11" s="69"/>
+      <c r="P11" s="69"/>
+    </row>
+    <row r="12" spans="2:16" ht="27.95" customHeight="1">
+      <c r="B12" s="55">
         <f>SUM(Table_Tracker[Total Keys])</f>
         <v>529</v>
       </c>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
       <c r="E12" s="15"/>
-      <c r="F12" s="68">
+      <c r="F12" s="50">
         <f>SUM(Table_Tracker[Spare Keys (BMS)])</f>
         <v>372</v>
       </c>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
       <c r="I12" s="15"/>
-      <c r="J12" s="59">
+      <c r="J12" s="58">
         <f>SUM(Table_Tracker[Issued Keys])</f>
         <v>95</v>
       </c>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="69"/>
       <c r="M12" s="15"/>
-      <c r="N12" s="75">
+      <c r="N12" s="52">
         <f>SUM(Table_Tracker[Missing Keys])</f>
         <v>68</v>
       </c>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-    </row>
-    <row r="13" spans="2:16" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="44" t="s">
+      <c r="O12" s="69"/>
+      <c r="P12" s="69"/>
+    </row>
+    <row r="13" spans="2:16" ht="15.95" customHeight="1">
+      <c r="B13" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="15"/>
-      <c r="F13" s="52" t="s">
+      <c r="F13" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
       <c r="I13" s="15"/>
-      <c r="J13" s="74" t="s">
+      <c r="J13" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
+      <c r="K13" s="69"/>
+      <c r="L13" s="69"/>
       <c r="M13" s="15"/>
-      <c r="N13" s="53" t="s">
+      <c r="N13" s="66" t="s">
         <v>22</v>
       </c>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-    </row>
-    <row r="15" spans="2:16" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="46" t="s">
+      <c r="O13" s="69"/>
+      <c r="P13" s="69"/>
+    </row>
+    <row r="15" spans="2:16" ht="21.95" customHeight="1">
+      <c r="B15" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="48"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="70"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="71"/>
       <c r="I15" s="15"/>
-      <c r="J15" s="63" t="s">
+      <c r="J15" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-    </row>
-    <row r="16" spans="2:16" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K15" s="69"/>
+      <c r="L15" s="69"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="69"/>
+    </row>
+    <row r="16" spans="2:16" ht="21.95" customHeight="1">
       <c r="B16" s="16" t="s">
         <v>25</v>
       </c>
@@ -3171,7 +3184,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="18" customHeight="1">
       <c r="B17" s="17" t="s">
         <v>39</v>
       </c>
@@ -3228,7 +3241,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="18" customHeight="1">
       <c r="B18" s="17" t="s">
         <v>41</v>
       </c>
@@ -3285,7 +3298,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="18" customHeight="1">
       <c r="B19" s="17" t="s">
         <v>43</v>
       </c>
@@ -3342,7 +3355,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" ht="18" customHeight="1">
       <c r="B20" s="17" t="s">
         <v>45</v>
       </c>
@@ -3399,7 +3412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="18" customHeight="1">
       <c r="B21" s="17" t="s">
         <v>47</v>
       </c>
@@ -3456,7 +3469,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" ht="20.100000000000001" customHeight="1">
       <c r="B22" s="17" t="s">
         <v>49</v>
       </c>
@@ -3513,7 +3526,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="18" customHeight="1">
       <c r="B23" s="17" t="s">
         <v>51</v>
       </c>
@@ -3550,7 +3563,7 @@
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
     </row>
-    <row r="24" spans="2:16" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="21.95" customHeight="1">
       <c r="B24" s="17" t="s">
         <v>52</v>
       </c>
@@ -3579,17 +3592,17 @@
         <v>1</v>
       </c>
       <c r="I24" s="15"/>
-      <c r="J24" s="63" t="s">
+      <c r="J24" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="K24" s="43"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
-    </row>
-    <row r="25" spans="2:16" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K24" s="69"/>
+      <c r="L24" s="69"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="69"/>
+      <c r="O24" s="69"/>
+      <c r="P24" s="69"/>
+    </row>
+    <row r="25" spans="2:16" ht="21.95" customHeight="1">
       <c r="B25" s="17" t="s">
         <v>54</v>
       </c>
@@ -3621,22 +3634,22 @@
       <c r="J25" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="K25" s="60" t="s">
+      <c r="K25" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="L25" s="61"/>
+      <c r="L25" s="72"/>
       <c r="M25" s="3" t="s">
         <v>37</v>
       </c>
       <c r="N25" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="O25" s="60" t="s">
+      <c r="O25" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="P25" s="61"/>
-    </row>
-    <row r="26" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P25" s="72"/>
+    </row>
+    <row r="26" spans="2:16" ht="18" customHeight="1">
       <c r="B26" s="17" t="s">
         <v>59</v>
       </c>
@@ -3668,22 +3681,22 @@
       <c r="J26" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="K26" s="40" t="s">
+      <c r="K26" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="L26" s="41"/>
+      <c r="L26" s="73"/>
       <c r="M26" s="5">
         <v>22</v>
       </c>
       <c r="N26" s="5">
         <v>22</v>
       </c>
-      <c r="O26" s="57" t="s">
+      <c r="O26" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="P26" s="41"/>
-    </row>
-    <row r="27" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P26" s="73"/>
+    </row>
+    <row r="27" spans="2:16" ht="18" customHeight="1">
       <c r="B27" s="17" t="s">
         <v>63</v>
       </c>
@@ -3715,22 +3728,22 @@
       <c r="J27" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="K27" s="40" t="s">
+      <c r="K27" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="L27" s="41"/>
+      <c r="L27" s="73"/>
       <c r="M27" s="5">
         <v>15</v>
       </c>
       <c r="N27" s="5">
         <v>15</v>
       </c>
-      <c r="O27" s="57" t="s">
+      <c r="O27" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="P27" s="41"/>
-    </row>
-    <row r="28" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P27" s="73"/>
+    </row>
+    <row r="28" spans="2:16" ht="18" customHeight="1">
       <c r="B28" s="17" t="s">
         <v>66</v>
       </c>
@@ -3762,22 +3775,22 @@
       <c r="J28" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="K28" s="40" t="s">
+      <c r="K28" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="L28" s="41"/>
+      <c r="L28" s="73"/>
       <c r="M28" s="5">
         <v>9</v>
       </c>
       <c r="N28" s="5">
         <v>9</v>
       </c>
-      <c r="O28" s="57" t="s">
+      <c r="O28" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="P28" s="41"/>
-    </row>
-    <row r="29" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P28" s="73"/>
+    </row>
+    <row r="29" spans="2:16" ht="18" customHeight="1">
       <c r="B29" s="17" t="s">
         <v>69</v>
       </c>
@@ -3809,22 +3822,22 @@
       <c r="J29" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="K29" s="40" t="s">
+      <c r="K29" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="L29" s="41"/>
+      <c r="L29" s="73"/>
       <c r="M29" s="5">
         <v>6</v>
       </c>
       <c r="N29" s="5">
         <v>6</v>
       </c>
-      <c r="O29" s="57" t="s">
+      <c r="O29" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="P29" s="41"/>
-    </row>
-    <row r="30" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P29" s="73"/>
+    </row>
+    <row r="30" spans="2:16" ht="18" customHeight="1">
       <c r="B30" s="17" t="s">
         <v>73</v>
       </c>
@@ -3856,22 +3869,22 @@
       <c r="J30" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="K30" s="40" t="s">
+      <c r="K30" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="L30" s="41"/>
+      <c r="L30" s="73"/>
       <c r="M30" s="5">
         <v>4</v>
       </c>
       <c r="N30" s="5">
         <v>4</v>
       </c>
-      <c r="O30" s="57" t="s">
+      <c r="O30" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="P30" s="41"/>
-    </row>
-    <row r="31" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P30" s="73"/>
+    </row>
+    <row r="31" spans="2:16" ht="18" customHeight="1">
       <c r="B31" s="19" t="s">
         <v>76</v>
       </c>
@@ -3903,22 +3916,22 @@
       <c r="J31" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K31" s="40" t="s">
+      <c r="K31" s="48" t="s">
         <v>78</v>
       </c>
-      <c r="L31" s="41"/>
+      <c r="L31" s="73"/>
       <c r="M31" s="5">
         <v>23</v>
       </c>
       <c r="N31" s="5">
         <v>23</v>
       </c>
-      <c r="O31" s="57" t="s">
+      <c r="O31" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="P31" s="41"/>
-    </row>
-    <row r="32" spans="2:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P31" s="73"/>
+    </row>
+    <row r="32" spans="2:16" ht="20.100000000000001" customHeight="1">
       <c r="B32" s="15"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
@@ -3930,10 +3943,10 @@
       <c r="J32" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="K32" s="64" t="s">
+      <c r="K32" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="L32" s="65"/>
+      <c r="L32" s="74"/>
       <c r="M32" s="7">
         <f>SUM(M26:M31)</f>
         <v>79</v>
@@ -3942,31 +3955,31 @@
         <f>SUM(N26:N31)</f>
         <v>79</v>
       </c>
-      <c r="O32" s="64" t="s">
+      <c r="O32" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="P32" s="65"/>
-    </row>
-    <row r="34" spans="2:16" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="63" t="s">
+      <c r="P32" s="74"/>
+    </row>
+    <row r="34" spans="2:16" ht="21.95" customHeight="1">
+      <c r="B34" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="43"/>
-      <c r="N34" s="43"/>
-      <c r="O34" s="43"/>
-      <c r="P34" s="43"/>
-    </row>
-    <row r="35" spans="2:16" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C34" s="69"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="69"/>
+      <c r="K34" s="69"/>
+      <c r="L34" s="69"/>
+      <c r="M34" s="69"/>
+      <c r="N34" s="69"/>
+      <c r="O34" s="69"/>
+      <c r="P34" s="69"/>
+    </row>
+    <row r="35" spans="2:16" ht="21.95" customHeight="1">
       <c r="B35" s="3" t="s">
         <v>83</v>
       </c>
@@ -3979,27 +3992,27 @@
       <c r="E35" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F35" s="60" t="s">
+      <c r="F35" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="G35" s="61"/>
-      <c r="H35" s="60" t="s">
+      <c r="G35" s="72"/>
+      <c r="H35" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="I35" s="70"/>
-      <c r="J35" s="70"/>
-      <c r="K35" s="70"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="61"/>
+      <c r="I35" s="75"/>
+      <c r="J35" s="75"/>
+      <c r="K35" s="75"/>
+      <c r="L35" s="75"/>
+      <c r="M35" s="72"/>
       <c r="N35" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O35" s="60" t="s">
+      <c r="O35" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="P35" s="61"/>
-    </row>
-    <row r="36" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P35" s="72"/>
+    </row>
+    <row r="36" spans="2:16" ht="18.95" customHeight="1">
       <c r="B36" s="8" t="s">
         <v>90</v>
       </c>
@@ -4012,27 +4025,27 @@
       <c r="E36" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F36" s="40" t="s">
+      <c r="F36" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="G36" s="41"/>
-      <c r="H36" s="40" t="s">
+      <c r="G36" s="73"/>
+      <c r="H36" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="I36" s="62"/>
-      <c r="J36" s="62"/>
-      <c r="K36" s="62"/>
-      <c r="L36" s="62"/>
-      <c r="M36" s="41"/>
+      <c r="I36" s="76"/>
+      <c r="J36" s="76"/>
+      <c r="K36" s="76"/>
+      <c r="L36" s="76"/>
+      <c r="M36" s="73"/>
       <c r="N36" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="O36" s="57" t="s">
+      <c r="O36" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="P36" s="41"/>
-    </row>
-    <row r="37" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P36" s="73"/>
+    </row>
+    <row r="37" spans="2:16" ht="18.95" customHeight="1">
       <c r="B37" s="8" t="s">
         <v>96</v>
       </c>
@@ -4045,27 +4058,27 @@
       <c r="E37" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F37" s="40" t="s">
+      <c r="F37" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="G37" s="41"/>
-      <c r="H37" s="40" t="s">
+      <c r="G37" s="73"/>
+      <c r="H37" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="I37" s="62"/>
-      <c r="J37" s="62"/>
-      <c r="K37" s="62"/>
-      <c r="L37" s="62"/>
-      <c r="M37" s="41"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="76"/>
+      <c r="K37" s="76"/>
+      <c r="L37" s="76"/>
+      <c r="M37" s="73"/>
       <c r="N37" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="O37" s="57" t="s">
+      <c r="O37" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="P37" s="41"/>
-    </row>
-    <row r="38" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P37" s="73"/>
+    </row>
+    <row r="38" spans="2:16" ht="18.95" customHeight="1">
       <c r="B38" s="8" t="s">
         <v>98</v>
       </c>
@@ -4078,27 +4091,27 @@
       <c r="E38" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F38" s="40" t="s">
+      <c r="F38" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="G38" s="41"/>
-      <c r="H38" s="40" t="s">
+      <c r="G38" s="73"/>
+      <c r="H38" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="I38" s="62"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="62"/>
-      <c r="M38" s="41"/>
+      <c r="I38" s="76"/>
+      <c r="J38" s="76"/>
+      <c r="K38" s="76"/>
+      <c r="L38" s="76"/>
+      <c r="M38" s="73"/>
       <c r="N38" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="O38" s="57" t="s">
+      <c r="O38" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="P38" s="41"/>
-    </row>
-    <row r="39" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P38" s="73"/>
+    </row>
+    <row r="39" spans="2:16" ht="18.95" customHeight="1">
       <c r="B39" s="8" t="s">
         <v>101</v>
       </c>
@@ -4111,27 +4124,27 @@
       <c r="E39" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F39" s="40" t="s">
+      <c r="F39" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="G39" s="41"/>
-      <c r="H39" s="40" t="s">
+      <c r="G39" s="73"/>
+      <c r="H39" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="I39" s="62"/>
-      <c r="J39" s="62"/>
-      <c r="K39" s="62"/>
-      <c r="L39" s="62"/>
-      <c r="M39" s="41"/>
+      <c r="I39" s="76"/>
+      <c r="J39" s="76"/>
+      <c r="K39" s="76"/>
+      <c r="L39" s="76"/>
+      <c r="M39" s="73"/>
       <c r="N39" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="O39" s="57" t="s">
+      <c r="O39" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="P39" s="41"/>
-    </row>
-    <row r="40" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P39" s="73"/>
+    </row>
+    <row r="40" spans="2:16" ht="18.95" customHeight="1">
       <c r="B40" s="8" t="s">
         <v>104</v>
       </c>
@@ -4144,27 +4157,27 @@
       <c r="E40" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="40" t="s">
+      <c r="F40" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="G40" s="41"/>
-      <c r="H40" s="40" t="s">
+      <c r="G40" s="73"/>
+      <c r="H40" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="I40" s="62"/>
-      <c r="J40" s="62"/>
-      <c r="K40" s="62"/>
-      <c r="L40" s="62"/>
-      <c r="M40" s="41"/>
+      <c r="I40" s="76"/>
+      <c r="J40" s="76"/>
+      <c r="K40" s="76"/>
+      <c r="L40" s="76"/>
+      <c r="M40" s="73"/>
       <c r="N40" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="O40" s="57" t="s">
+      <c r="O40" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="P40" s="41"/>
-    </row>
-    <row r="41" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P40" s="73"/>
+    </row>
+    <row r="41" spans="2:16" ht="18.95" customHeight="1">
       <c r="B41" s="8" t="s">
         <v>110</v>
       </c>
@@ -4177,27 +4190,27 @@
       <c r="E41" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F41" s="40" t="s">
+      <c r="F41" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="G41" s="41"/>
-      <c r="H41" s="40" t="s">
+      <c r="G41" s="73"/>
+      <c r="H41" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="I41" s="62"/>
-      <c r="J41" s="62"/>
-      <c r="K41" s="62"/>
-      <c r="L41" s="62"/>
-      <c r="M41" s="41"/>
+      <c r="I41" s="76"/>
+      <c r="J41" s="76"/>
+      <c r="K41" s="76"/>
+      <c r="L41" s="76"/>
+      <c r="M41" s="73"/>
       <c r="N41" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="O41" s="57" t="s">
+      <c r="O41" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="P41" s="41"/>
-    </row>
-    <row r="42" spans="2:16" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P41" s="73"/>
+    </row>
+    <row r="42" spans="2:16" ht="18.95" customHeight="1">
       <c r="B42" s="8" t="s">
         <v>114</v>
       </c>
@@ -4210,28 +4223,82 @@
       <c r="E42" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F42" s="40" t="s">
+      <c r="F42" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="G42" s="41"/>
-      <c r="H42" s="40" t="s">
+      <c r="G42" s="73"/>
+      <c r="H42" s="48" t="s">
         <v>117</v>
       </c>
-      <c r="I42" s="62"/>
-      <c r="J42" s="62"/>
-      <c r="K42" s="62"/>
-      <c r="L42" s="62"/>
-      <c r="M42" s="41"/>
+      <c r="I42" s="76"/>
+      <c r="J42" s="76"/>
+      <c r="K42" s="76"/>
+      <c r="L42" s="76"/>
+      <c r="M42" s="73"/>
       <c r="N42" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="O42" s="57" t="s">
+      <c r="O42" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="P42" s="41"/>
+      <c r="P42" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="70">
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="J11:L11"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="J12:L12"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="H39:M39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="O39:P39"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="B34:P34"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="H37:M37"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="H36:M36"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="H38:M38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H41:M41"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="H40:M40"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="O41:P41"/>
     <mergeCell ref="B4:P4"/>
     <mergeCell ref="O37:P37"/>
     <mergeCell ref="J24:P24"/>
@@ -4248,60 +4315,6 @@
     <mergeCell ref="N12:P12"/>
     <mergeCell ref="F7:H7"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="B5:P5"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="O42:P42"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="H38:M38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H41:M41"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="H40:M40"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="O41:P41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="H39:M39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="O39:P39"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="B34:P34"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="H37:M37"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="H36:M36"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F9:H9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B2" location="'📊 Dashboard'!A1" display="📊 Executive Dashboard" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -4320,27 +4333,27 @@
     <tabColor rgb="FF008080"/>
   </sheetPr>
   <dimension ref="A1:P267"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" customWidth="1"/>
-    <col min="2" max="2" width="18.7265625" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" customWidth="1"/>
-    <col min="5" max="5" width="31.26953125" customWidth="1"/>
-    <col min="6" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" customWidth="1"/>
-    <col min="9" max="9" width="14.7265625" customWidth="1"/>
-    <col min="10" max="10" width="20.7265625" customWidth="1"/>
-    <col min="11" max="11" width="26.7265625" customWidth="1"/>
-    <col min="12" max="12" width="20.7265625" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="26.7109375" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
     <col min="13" max="13" width="24" style="30" customWidth="1"/>
-    <col min="14" max="14" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="38.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.81640625" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16">
       <c r="A1" s="15" t="s">
         <v>118</v>
       </c>
@@ -4360,7 +4373,7 @@
       <c r="O1" s="15"/>
       <c r="P1" s="15"/>
     </row>
-    <row r="2" spans="1:16" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="17.100000000000001" customHeight="1">
       <c r="A2" s="15"/>
       <c r="B2" s="2" t="s">
         <v>0</v>
@@ -4388,7 +4401,7 @@
       <c r="O2" s="15"/>
       <c r="P2" s="15"/>
     </row>
-    <row r="4" spans="1:16" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="27" customHeight="1" thickBot="1">
       <c r="A4" s="31" t="s">
         <v>119</v>
       </c>
@@ -4408,7 +4421,7 @@
       <c r="O4" s="31"/>
       <c r="P4" s="31"/>
     </row>
-    <row r="5" spans="1:16" ht="34" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="33.950000000000003" customHeight="1" thickBot="1">
       <c r="A5" s="32" t="s">
         <v>120</v>
       </c>
@@ -4436,7 +4449,7 @@
       <c r="O5" s="37"/>
       <c r="P5" s="37"/>
     </row>
-    <row r="6" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="24.95" customHeight="1">
       <c r="A6" s="35" t="s">
         <v>122</v>
       </c>
@@ -4468,7 +4481,7 @@
       <c r="O6" s="33"/>
       <c r="P6" s="33"/>
     </row>
-    <row r="7" spans="1:16" s="11" customFormat="1" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" s="11" customFormat="1" ht="29.1" customHeight="1">
       <c r="A7" s="21" t="s">
         <v>123</v>
       </c>
@@ -4518,7 +4531,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" hidden="1">
       <c r="A8" s="23">
         <v>1</v>
       </c>
@@ -4571,7 +4584,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" hidden="1">
       <c r="A9" s="23">
         <v>2</v>
       </c>
@@ -4624,7 +4637,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" hidden="1">
       <c r="A10" s="23">
         <v>3</v>
       </c>
@@ -4677,7 +4690,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" hidden="1">
       <c r="A11" s="23">
         <v>4</v>
       </c>
@@ -4730,7 +4743,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" hidden="1">
       <c r="A12" s="23">
         <v>5</v>
       </c>
@@ -4783,7 +4796,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" hidden="1">
       <c r="A13" s="23">
         <v>6</v>
       </c>
@@ -4836,7 +4849,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" hidden="1">
       <c r="A14" s="23">
         <v>7</v>
       </c>
@@ -4889,7 +4902,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" hidden="1">
       <c r="A15" s="23">
         <v>8</v>
       </c>
@@ -4942,7 +4955,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" hidden="1">
       <c r="A16" s="23">
         <v>9</v>
       </c>
@@ -4995,7 +5008,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" hidden="1">
       <c r="A17" s="23">
         <v>10</v>
       </c>
@@ -5048,7 +5061,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" hidden="1">
       <c r="A18" s="23">
         <v>11</v>
       </c>
@@ -5101,7 +5114,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" hidden="1">
       <c r="A19" s="23">
         <v>12</v>
       </c>
@@ -5154,7 +5167,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" hidden="1">
       <c r="A20" s="23">
         <v>13</v>
       </c>
@@ -5207,7 +5220,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" hidden="1">
       <c r="A21" s="23">
         <v>14</v>
       </c>
@@ -5260,7 +5273,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" hidden="1">
       <c r="A22" s="23">
         <v>15</v>
       </c>
@@ -5313,7 +5326,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" hidden="1">
       <c r="A23" s="23">
         <v>16</v>
       </c>
@@ -5366,7 +5379,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" hidden="1">
       <c r="A24" s="23">
         <v>17</v>
       </c>
@@ -5419,7 +5432,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" hidden="1">
       <c r="A25" s="23">
         <v>18</v>
       </c>
@@ -5472,7 +5485,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" hidden="1">
       <c r="A26" s="23">
         <v>19</v>
       </c>
@@ -5525,7 +5538,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" hidden="1">
       <c r="A27" s="23">
         <v>20</v>
       </c>
@@ -5578,7 +5591,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" hidden="1">
       <c r="A28" s="23">
         <v>21</v>
       </c>
@@ -5631,7 +5644,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" hidden="1">
       <c r="A29" s="23">
         <v>22</v>
       </c>
@@ -5684,7 +5697,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" hidden="1">
       <c r="A30" s="23">
         <v>23</v>
       </c>
@@ -5737,7 +5750,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" hidden="1">
       <c r="A31" s="23">
         <v>24</v>
       </c>
@@ -5790,7 +5803,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" hidden="1">
       <c r="A32" s="23">
         <v>25</v>
       </c>
@@ -5843,7 +5856,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" hidden="1">
       <c r="A33" s="23">
         <v>26</v>
       </c>
@@ -5896,7 +5909,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" hidden="1">
       <c r="A34" s="23">
         <v>27</v>
       </c>
@@ -5949,7 +5962,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" hidden="1">
       <c r="A35" s="23">
         <v>28</v>
       </c>
@@ -6002,7 +6015,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" hidden="1">
       <c r="A36" s="23">
         <v>29</v>
       </c>
@@ -6055,7 +6068,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" hidden="1">
       <c r="A37" s="23">
         <v>30</v>
       </c>
@@ -6108,7 +6121,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" hidden="1">
       <c r="A38" s="23">
         <v>31</v>
       </c>
@@ -6161,7 +6174,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" hidden="1">
       <c r="A39" s="23">
         <v>32</v>
       </c>
@@ -6214,7 +6227,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" hidden="1">
       <c r="A40" s="23">
         <v>33</v>
       </c>
@@ -6267,7 +6280,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" hidden="1">
       <c r="A41" s="23">
         <v>34</v>
       </c>
@@ -6320,7 +6333,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" hidden="1">
       <c r="A42" s="23">
         <v>35</v>
       </c>
@@ -6373,7 +6386,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" hidden="1">
       <c r="A43" s="23">
         <v>36</v>
       </c>
@@ -6426,7 +6439,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" hidden="1">
       <c r="A44" s="23">
         <v>37</v>
       </c>
@@ -6479,7 +6492,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" hidden="1">
       <c r="A45" s="23">
         <v>38</v>
       </c>
@@ -6532,7 +6545,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" hidden="1">
       <c r="A46" s="23">
         <v>39</v>
       </c>
@@ -6585,7 +6598,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" hidden="1">
       <c r="A47" s="23">
         <v>40</v>
       </c>
@@ -6638,7 +6651,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" hidden="1">
       <c r="A48" s="23">
         <v>41</v>
       </c>
@@ -6691,7 +6704,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" hidden="1">
       <c r="A49" s="23">
         <v>42</v>
       </c>
@@ -6744,7 +6757,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" hidden="1">
       <c r="A50" s="23">
         <v>43</v>
       </c>
@@ -6797,7 +6810,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" hidden="1">
       <c r="A51" s="23">
         <v>44</v>
       </c>
@@ -6850,7 +6863,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" hidden="1">
       <c r="A52" s="23">
         <v>45</v>
       </c>
@@ -6903,7 +6916,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" hidden="1">
       <c r="A53" s="23">
         <v>46</v>
       </c>
@@ -6956,7 +6969,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" hidden="1">
       <c r="A54" s="23">
         <v>47</v>
       </c>
@@ -7009,7 +7022,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" hidden="1">
       <c r="A55" s="23">
         <v>48</v>
       </c>
@@ -7062,7 +7075,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" hidden="1">
       <c r="A56" s="23">
         <v>49</v>
       </c>
@@ -7115,7 +7128,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" hidden="1">
       <c r="A57" s="23">
         <v>50</v>
       </c>
@@ -7166,7 +7179,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" hidden="1">
       <c r="A58" s="23">
         <v>51</v>
       </c>
@@ -7219,7 +7232,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" hidden="1">
       <c r="A59" s="23">
         <v>52</v>
       </c>
@@ -7272,7 +7285,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" hidden="1">
       <c r="A60" s="23">
         <v>53</v>
       </c>
@@ -7325,7 +7338,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16" hidden="1">
       <c r="A61" s="23">
         <v>54</v>
       </c>
@@ -7378,7 +7391,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" hidden="1">
       <c r="A62" s="23">
         <v>55</v>
       </c>
@@ -7431,7 +7444,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" hidden="1">
       <c r="A63" s="23">
         <v>56</v>
       </c>
@@ -7484,7 +7497,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" hidden="1">
       <c r="A64" s="23">
         <v>57</v>
       </c>
@@ -7537,7 +7550,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" hidden="1">
       <c r="A65" s="23">
         <v>58</v>
       </c>
@@ -7590,7 +7603,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:16" hidden="1">
       <c r="A66" s="23">
         <v>59</v>
       </c>
@@ -7643,7 +7656,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:16" hidden="1">
       <c r="A67" s="23">
         <v>60</v>
       </c>
@@ -7694,7 +7707,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" hidden="1">
       <c r="A68" s="23">
         <v>61</v>
       </c>
@@ -7745,7 +7758,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:16" hidden="1">
       <c r="A69" s="23">
         <v>62</v>
       </c>
@@ -7798,7 +7811,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:16" hidden="1">
       <c r="A70" s="23">
         <v>63</v>
       </c>
@@ -7851,7 +7864,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:16" hidden="1">
       <c r="A71" s="23">
         <v>64</v>
       </c>
@@ -7904,7 +7917,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:16" hidden="1">
       <c r="A72" s="23">
         <v>65</v>
       </c>
@@ -7957,7 +7970,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:16" hidden="1">
       <c r="A73" s="23">
         <v>66</v>
       </c>
@@ -8008,7 +8021,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:16" hidden="1">
       <c r="A74" s="23">
         <v>67</v>
       </c>
@@ -8059,7 +8072,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16" hidden="1">
       <c r="A75" s="23">
         <v>68</v>
       </c>
@@ -8112,7 +8125,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:16" hidden="1">
       <c r="A76" s="23">
         <v>69</v>
       </c>
@@ -8165,7 +8178,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:16" hidden="1">
       <c r="A77" s="23">
         <v>70</v>
       </c>
@@ -8218,7 +8231,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:16" hidden="1">
       <c r="A78" s="23">
         <v>71</v>
       </c>
@@ -8271,7 +8284,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16" hidden="1">
       <c r="A79" s="23">
         <v>72</v>
       </c>
@@ -8322,7 +8335,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:16" hidden="1">
       <c r="A80" s="23">
         <v>73</v>
       </c>
@@ -8375,7 +8388,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" hidden="1">
       <c r="A81" s="23">
         <v>74</v>
       </c>
@@ -8426,7 +8439,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" hidden="1">
       <c r="A82" s="23">
         <v>75</v>
       </c>
@@ -8477,7 +8490,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" hidden="1">
       <c r="A83" s="23">
         <v>76</v>
       </c>
@@ -8528,7 +8541,7 @@
         <v>⚠️ KEY DAMAGED / REPLACE</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" hidden="1">
       <c r="A84" s="23">
         <v>77</v>
       </c>
@@ -8579,7 +8592,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" hidden="1">
       <c r="A85" s="23">
         <v>78</v>
       </c>
@@ -8630,7 +8643,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" hidden="1">
       <c r="A86" s="23">
         <v>79</v>
       </c>
@@ -8683,7 +8696,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" hidden="1">
       <c r="A87" s="23">
         <v>80</v>
       </c>
@@ -8736,7 +8749,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" hidden="1">
       <c r="A88" s="23">
         <v>81</v>
       </c>
@@ -8789,7 +8802,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" hidden="1">
       <c r="A89" s="23">
         <v>82</v>
       </c>
@@ -8842,7 +8855,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" hidden="1">
       <c r="A90" s="23">
         <v>83</v>
       </c>
@@ -8895,7 +8908,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" hidden="1">
       <c r="A91" s="23">
         <v>84</v>
       </c>
@@ -8948,7 +8961,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" hidden="1">
       <c r="A92" s="23">
         <v>85</v>
       </c>
@@ -9001,7 +9014,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" hidden="1">
       <c r="A93" s="23">
         <v>86</v>
       </c>
@@ -9054,7 +9067,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" hidden="1">
       <c r="A94" s="23">
         <v>87</v>
       </c>
@@ -9105,7 +9118,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" hidden="1">
       <c r="A95" s="23">
         <v>88</v>
       </c>
@@ -9156,7 +9169,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" hidden="1">
       <c r="A96" s="23">
         <v>89</v>
       </c>
@@ -9209,7 +9222,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" hidden="1">
       <c r="A97" s="23">
         <v>90</v>
       </c>
@@ -9262,7 +9275,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" hidden="1">
       <c r="A98" s="23">
         <v>91</v>
       </c>
@@ -9315,7 +9328,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" hidden="1">
       <c r="A99" s="23">
         <v>92</v>
       </c>
@@ -9368,7 +9381,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16" hidden="1">
       <c r="A100" s="23">
         <v>93</v>
       </c>
@@ -9421,7 +9434,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16" hidden="1">
       <c r="A101" s="23">
         <v>94</v>
       </c>
@@ -9472,7 +9485,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" hidden="1">
       <c r="A102" s="23">
         <v>95</v>
       </c>
@@ -9525,7 +9538,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" hidden="1">
       <c r="A103" s="23">
         <v>96</v>
       </c>
@@ -9576,7 +9589,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" hidden="1">
       <c r="A104" s="23">
         <v>97</v>
       </c>
@@ -9627,7 +9640,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" hidden="1">
       <c r="A105" s="23">
         <v>98</v>
       </c>
@@ -9680,7 +9693,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" hidden="1">
       <c r="A106" s="23">
         <v>99</v>
       </c>
@@ -9733,7 +9746,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16" hidden="1">
       <c r="A107" s="23">
         <v>100</v>
       </c>
@@ -9786,7 +9799,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:16" hidden="1">
       <c r="A108" s="23">
         <v>101</v>
       </c>
@@ -9839,7 +9852,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:16" hidden="1">
       <c r="A109" s="23">
         <v>102</v>
       </c>
@@ -9892,7 +9905,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" hidden="1">
       <c r="A110" s="23">
         <v>103</v>
       </c>
@@ -9945,7 +9958,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16" hidden="1">
       <c r="A111" s="23">
         <v>104</v>
       </c>
@@ -9998,7 +10011,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16" hidden="1">
       <c r="A112" s="23">
         <v>105</v>
       </c>
@@ -10051,7 +10064,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:16" hidden="1">
       <c r="A113" s="23">
         <v>106</v>
       </c>
@@ -10104,7 +10117,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:16" hidden="1">
       <c r="A114" s="23">
         <v>107</v>
       </c>
@@ -10155,7 +10168,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:16" hidden="1">
       <c r="A115" s="23">
         <v>108</v>
       </c>
@@ -10208,7 +10221,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" hidden="1">
       <c r="A116" s="23">
         <v>109</v>
       </c>
@@ -10261,7 +10274,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" hidden="1">
       <c r="A117" s="23">
         <v>110</v>
       </c>
@@ -10314,7 +10327,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" hidden="1">
       <c r="A118" s="23">
         <v>111</v>
       </c>
@@ -10367,7 +10380,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" hidden="1">
       <c r="A119" s="23">
         <v>112</v>
       </c>
@@ -10418,7 +10431,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16" hidden="1">
       <c r="A120" s="23">
         <v>113</v>
       </c>
@@ -10469,7 +10482,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" hidden="1">
       <c r="A121" s="23">
         <v>114</v>
       </c>
@@ -10520,7 +10533,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16" hidden="1">
       <c r="A122" s="23">
         <v>115</v>
       </c>
@@ -10573,7 +10586,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16" hidden="1">
       <c r="A123" s="23">
         <v>116</v>
       </c>
@@ -10626,7 +10639,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" hidden="1">
       <c r="A124" s="23">
         <v>117</v>
       </c>
@@ -10677,7 +10690,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" hidden="1">
       <c r="A125" s="23">
         <v>118</v>
       </c>
@@ -10728,7 +10741,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16" hidden="1">
       <c r="A126" s="23">
         <v>119</v>
       </c>
@@ -10779,7 +10792,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:16" hidden="1">
       <c r="A127" s="23">
         <v>120</v>
       </c>
@@ -10830,7 +10843,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:16" hidden="1">
       <c r="A128" s="23">
         <v>121</v>
       </c>
@@ -10881,7 +10894,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:16" hidden="1">
       <c r="A129" s="23">
         <v>122</v>
       </c>
@@ -10932,7 +10945,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16" hidden="1">
       <c r="A130" s="23">
         <v>123</v>
       </c>
@@ -10983,7 +10996,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:16" hidden="1">
       <c r="A131" s="23">
         <v>124</v>
       </c>
@@ -11036,7 +11049,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" hidden="1">
       <c r="A132" s="23">
         <v>125</v>
       </c>
@@ -11089,7 +11102,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:16" hidden="1">
       <c r="A133" s="23">
         <v>126</v>
       </c>
@@ -11142,7 +11155,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:16" hidden="1">
       <c r="A134" s="23">
         <v>127</v>
       </c>
@@ -11195,7 +11208,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:16" hidden="1">
       <c r="A135" s="23">
         <v>128</v>
       </c>
@@ -11248,7 +11261,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16" hidden="1">
       <c r="A136" s="23">
         <v>129</v>
       </c>
@@ -11299,7 +11312,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:16" hidden="1">
       <c r="A137" s="23">
         <v>130</v>
       </c>
@@ -11352,7 +11365,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16" hidden="1">
       <c r="A138" s="23">
         <v>131</v>
       </c>
@@ -11405,7 +11418,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16" hidden="1">
       <c r="A139" s="23">
         <v>132</v>
       </c>
@@ -11458,7 +11471,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16" hidden="1">
       <c r="A140" s="23">
         <v>133</v>
       </c>
@@ -11509,7 +11522,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16" hidden="1">
       <c r="A141" s="23">
         <v>134</v>
       </c>
@@ -11560,7 +11573,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" hidden="1">
       <c r="A142" s="23">
         <v>135</v>
       </c>
@@ -11611,7 +11624,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" hidden="1">
       <c r="A143" s="23">
         <v>136</v>
       </c>
@@ -11662,7 +11675,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" hidden="1">
       <c r="A144" s="23">
         <v>137</v>
       </c>
@@ -11713,7 +11726,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" hidden="1">
       <c r="A145" s="23">
         <v>138</v>
       </c>
@@ -11764,7 +11777,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" hidden="1">
       <c r="A146" s="23">
         <v>139</v>
       </c>
@@ -11817,7 +11830,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:16" hidden="1">
       <c r="A147" s="23">
         <v>140</v>
       </c>
@@ -11868,7 +11881,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16" hidden="1">
       <c r="A148" s="23">
         <v>141</v>
       </c>
@@ -11919,7 +11932,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16" hidden="1">
       <c r="A149" s="23">
         <v>142</v>
       </c>
@@ -11972,7 +11985,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" hidden="1">
       <c r="A150" s="23">
         <v>143</v>
       </c>
@@ -12025,7 +12038,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16" hidden="1">
       <c r="A151" s="23">
         <v>144</v>
       </c>
@@ -12078,7 +12091,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16" hidden="1">
       <c r="A152" s="23">
         <v>145</v>
       </c>
@@ -12131,7 +12144,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16" hidden="1">
       <c r="A153" s="23">
         <v>146</v>
       </c>
@@ -12184,7 +12197,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16" hidden="1">
       <c r="A154" s="23">
         <v>147</v>
       </c>
@@ -12237,7 +12250,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16" hidden="1">
       <c r="A155" s="23">
         <v>148</v>
       </c>
@@ -12290,7 +12303,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" hidden="1">
       <c r="A156" s="23">
         <v>149</v>
       </c>
@@ -12343,7 +12356,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" hidden="1">
       <c r="A157" s="23">
         <v>150</v>
       </c>
@@ -12396,7 +12409,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16" hidden="1">
       <c r="A158" s="23">
         <v>151</v>
       </c>
@@ -12435,7 +12448,9 @@
       <c r="L158" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="M158" s="28"/>
+      <c r="M158" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="N158" s="14" t="s">
         <v>34</v>
       </c>
@@ -12447,7 +12462,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" hidden="1">
       <c r="A159" s="23">
         <v>152</v>
       </c>
@@ -12486,7 +12501,9 @@
       <c r="L159" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="M159" s="28"/>
+      <c r="M159" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="N159" s="14" t="s">
         <v>34</v>
       </c>
@@ -12498,7 +12515,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16" hidden="1">
       <c r="A160" s="23">
         <v>153</v>
       </c>
@@ -12542,14 +12559,14 @@
         <v>34</v>
       </c>
       <c r="O160" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P160" s="14" t="str">
         <f t="shared" si="8"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:16" hidden="1">
       <c r="A161" s="23">
         <v>154</v>
       </c>
@@ -12593,14 +12610,14 @@
         <v>34</v>
       </c>
       <c r="O161" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P161" s="14" t="str">
         <f t="shared" si="8"/>
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:16" hidden="1">
       <c r="A162" s="23">
         <v>155</v>
       </c>
@@ -12639,19 +12656,21 @@
       <c r="L162" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="M162" s="28"/>
+      <c r="M162" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="N162" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O162" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P162" s="14" t="str">
         <f t="shared" si="8"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:16" hidden="1">
       <c r="A163" s="23">
         <v>156</v>
       </c>
@@ -12702,7 +12721,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16" hidden="1">
       <c r="A164" s="23">
         <v>157</v>
       </c>
@@ -12741,19 +12760,21 @@
       <c r="L164" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="M164" s="28"/>
+      <c r="M164" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="N164" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O164" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P164" s="14" t="str">
         <f t="shared" si="8"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:16" hidden="1">
       <c r="A165" s="23">
         <v>158</v>
       </c>
@@ -12792,7 +12813,9 @@
       <c r="L165" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="M165" s="28"/>
+      <c r="M165" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="N165" s="14" t="s">
         <v>35</v>
       </c>
@@ -12804,7 +12827,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:16" hidden="1">
       <c r="A166" s="23">
         <v>159</v>
       </c>
@@ -12843,7 +12866,9 @@
       <c r="L166" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="M166" s="28"/>
+      <c r="M166" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="N166" s="14" t="s">
         <v>34</v>
       </c>
@@ -12855,7 +12880,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16" hidden="1">
       <c r="A167" s="23">
         <v>160</v>
       </c>
@@ -12889,7 +12914,7 @@
         <v>⚠️ Missing Key</v>
       </c>
       <c r="K167" s="23" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L167" s="23" t="s">
         <v>63</v>
@@ -12899,14 +12924,14 @@
         <v>34</v>
       </c>
       <c r="O167" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P167" s="14" t="str">
         <f t="shared" si="8"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:16" hidden="1">
       <c r="A168" s="23">
         <v>161</v>
       </c>
@@ -12957,7 +12982,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16" hidden="1">
       <c r="A169" s="23">
         <v>162</v>
       </c>
@@ -13001,14 +13026,14 @@
         <v>34</v>
       </c>
       <c r="O169" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P169" s="14" t="str">
         <f t="shared" si="8"/>
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:16" hidden="1">
       <c r="A170" s="23">
         <v>163</v>
       </c>
@@ -13042,7 +13067,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K170" s="23" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L170" s="23" t="s">
         <v>63</v>
@@ -13059,7 +13084,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16" hidden="1">
       <c r="A171" s="23">
         <v>164</v>
       </c>
@@ -13093,7 +13118,7 @@
         <v>⚠️ Missing Key</v>
       </c>
       <c r="K171" s="23" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L171" s="23" t="s">
         <v>63</v>
@@ -13110,7 +13135,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16" hidden="1">
       <c r="A172" s="23">
         <v>165</v>
       </c>
@@ -13144,7 +13169,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K172" s="23" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="L172" s="23" t="s">
         <v>63</v>
@@ -13161,7 +13186,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16" hidden="1">
       <c r="A173" s="23">
         <v>166</v>
       </c>
@@ -13195,7 +13220,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K173" s="23" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L173" s="23" t="s">
         <v>63</v>
@@ -13212,7 +13237,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:16">
       <c r="A174" s="23">
         <v>167</v>
       </c>
@@ -13249,19 +13274,21 @@
       <c r="L174" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="M174" s="28"/>
+      <c r="M174" s="28" t="s">
+        <v>248</v>
+      </c>
       <c r="N174" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O174" s="14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P174" s="14" t="str">
         <f t="shared" si="8"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16" hidden="1">
       <c r="A175" s="23">
         <v>168</v>
       </c>
@@ -13295,7 +13322,7 @@
         <v>🔑 Issued to Staff</v>
       </c>
       <c r="K175" s="23" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L175" s="23" t="s">
         <v>63</v>
@@ -13312,7 +13339,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16" hidden="1">
       <c r="A176" s="23">
         <v>169</v>
       </c>
@@ -13351,19 +13378,21 @@
       <c r="L176" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="M176" s="28"/>
+      <c r="M176" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="N176" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O176" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P176" s="14" t="str">
         <f t="shared" si="8"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16" hidden="1">
       <c r="A177" s="23">
         <v>170</v>
       </c>
@@ -13402,19 +13431,21 @@
       <c r="L177" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="M177" s="28"/>
+      <c r="M177" s="28" t="s">
+        <v>236</v>
+      </c>
       <c r="N177" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O177" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P177" s="14" t="str">
         <f t="shared" si="8"/>
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16" hidden="1">
       <c r="A178" s="23">
         <v>171</v>
       </c>
@@ -13458,14 +13489,14 @@
         <v>34</v>
       </c>
       <c r="O178" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P178" s="14" t="str">
         <f t="shared" si="8"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="179" spans="1:16" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16" s="15" customFormat="1" hidden="1">
       <c r="A179" s="23">
         <v>172</v>
       </c>
@@ -13494,7 +13525,7 @@
         <v>0</v>
       </c>
       <c r="J179" s="23" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K179" s="23" t="s">
         <v>64</v>
@@ -13503,19 +13534,19 @@
         <v>137</v>
       </c>
       <c r="M179" s="28" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N179" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O179" s="14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="P179" s="14" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" hidden="1">
       <c r="A180" s="23">
         <v>173</v>
       </c>
@@ -13529,7 +13560,7 @@
         <v>30</v>
       </c>
       <c r="E180" s="23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F180" s="23">
         <v>2</v>
@@ -13559,14 +13590,14 @@
         <v>34</v>
       </c>
       <c r="O180" s="14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P180" s="14" t="str">
         <f t="shared" si="8"/>
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:16" hidden="1">
       <c r="A181" s="23">
         <v>174</v>
       </c>
@@ -13580,7 +13611,7 @@
         <v>30</v>
       </c>
       <c r="E181" s="23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F181" s="23">
         <v>2</v>
@@ -13610,14 +13641,14 @@
         <v>34</v>
       </c>
       <c r="O181" s="14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P181" s="14" t="str">
         <f t="shared" si="8"/>
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16" hidden="1">
       <c r="A182" s="23">
         <v>175</v>
       </c>
@@ -13631,7 +13662,7 @@
         <v>30</v>
       </c>
       <c r="E182" s="23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F182" s="23">
         <v>2</v>
@@ -13657,20 +13688,20 @@
         <v>137</v>
       </c>
       <c r="M182" s="28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N182" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O182" s="14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P182" s="14" t="str">
         <f t="shared" si="8"/>
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16" hidden="1">
       <c r="A183" s="23">
         <v>176</v>
       </c>
@@ -13684,7 +13715,7 @@
         <v>30</v>
       </c>
       <c r="E183" s="23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F183" s="23">
         <v>2</v>
@@ -13710,20 +13741,20 @@
         <v>137</v>
       </c>
       <c r="M183" s="28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N183" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O183" s="14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P183" s="14" t="str">
         <f t="shared" si="8"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16" hidden="1">
       <c r="A184" s="23">
         <v>177</v>
       </c>
@@ -13737,7 +13768,7 @@
         <v>30</v>
       </c>
       <c r="E184" s="23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F184" s="23">
         <v>2</v>
@@ -13757,26 +13788,26 @@
         <v>⚠️ Missing Key</v>
       </c>
       <c r="K184" s="23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L184" s="23" t="s">
         <v>137</v>
       </c>
       <c r="M184" s="28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N184" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O184" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P184" s="14" t="str">
         <f t="shared" si="8"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:16" hidden="1">
       <c r="A185" s="23">
         <v>178</v>
       </c>
@@ -13790,7 +13821,7 @@
         <v>31</v>
       </c>
       <c r="E185" s="23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F185" s="23">
         <v>3</v>
@@ -13817,7 +13848,7 @@
       </c>
       <c r="M185" s="28"/>
       <c r="N185" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O185" s="14" t="s">
         <v>139</v>
@@ -13827,7 +13858,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16" hidden="1">
       <c r="A186" s="23">
         <v>179</v>
       </c>
@@ -13841,7 +13872,7 @@
         <v>31</v>
       </c>
       <c r="E186" s="23" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F186" s="23">
         <v>3</v>
@@ -13868,7 +13899,7 @@
       </c>
       <c r="M186" s="28"/>
       <c r="N186" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O186" s="14" t="s">
         <v>139</v>
@@ -13878,7 +13909,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16" hidden="1">
       <c r="A187" s="23">
         <v>180</v>
       </c>
@@ -13892,7 +13923,7 @@
         <v>31</v>
       </c>
       <c r="E187" s="23" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F187" s="23">
         <v>3</v>
@@ -13919,7 +13950,7 @@
       </c>
       <c r="M187" s="28"/>
       <c r="N187" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O187" s="14" t="s">
         <v>139</v>
@@ -13929,7 +13960,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:16" hidden="1">
       <c r="A188" s="23">
         <v>181</v>
       </c>
@@ -13943,7 +13974,7 @@
         <v>31</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F188" s="23">
         <v>3</v>
@@ -13970,7 +14001,7 @@
       </c>
       <c r="M188" s="28"/>
       <c r="N188" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O188" s="14" t="s">
         <v>139</v>
@@ -13980,7 +14011,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:16" hidden="1">
       <c r="A189" s="23">
         <v>182</v>
       </c>
@@ -13994,7 +14025,7 @@
         <v>31</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F189" s="23">
         <v>3</v>
@@ -14021,7 +14052,7 @@
       </c>
       <c r="M189" s="28"/>
       <c r="N189" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O189" s="14" t="s">
         <v>139</v>
@@ -14031,7 +14062,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16" hidden="1">
       <c r="A190" s="23">
         <v>183</v>
       </c>
@@ -14045,7 +14076,7 @@
         <v>31</v>
       </c>
       <c r="E190" s="23" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F190" s="23">
         <v>3</v>
@@ -14072,7 +14103,7 @@
       </c>
       <c r="M190" s="28"/>
       <c r="N190" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O190" s="14" t="s">
         <v>139</v>
@@ -14082,7 +14113,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16" hidden="1">
       <c r="A191" s="23">
         <v>184</v>
       </c>
@@ -14096,7 +14127,7 @@
         <v>31</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F191" s="23">
         <v>3</v>
@@ -14123,7 +14154,7 @@
       </c>
       <c r="M191" s="28"/>
       <c r="N191" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O191" s="14" t="s">
         <v>139</v>
@@ -14133,7 +14164,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:16" hidden="1">
       <c r="A192" s="23">
         <v>185</v>
       </c>
@@ -14147,7 +14178,7 @@
         <v>31</v>
       </c>
       <c r="E192" s="23" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F192" s="23">
         <v>3</v>
@@ -14174,7 +14205,7 @@
       </c>
       <c r="M192" s="28"/>
       <c r="N192" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O192" s="14" t="s">
         <v>139</v>
@@ -14184,7 +14215,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:16" hidden="1">
       <c r="A193" s="23">
         <v>186</v>
       </c>
@@ -14198,7 +14229,7 @@
         <v>31</v>
       </c>
       <c r="E193" s="23" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F193" s="23">
         <v>3</v>
@@ -14225,7 +14256,7 @@
       </c>
       <c r="M193" s="28"/>
       <c r="N193" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O193" s="14" t="s">
         <v>139</v>
@@ -14235,7 +14266,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:16" hidden="1">
       <c r="A194" s="23">
         <v>187</v>
       </c>
@@ -14249,7 +14280,7 @@
         <v>31</v>
       </c>
       <c r="E194" s="23" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F194" s="23">
         <v>3</v>
@@ -14276,7 +14307,7 @@
       </c>
       <c r="M194" s="28"/>
       <c r="N194" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O194" s="14" t="s">
         <v>139</v>
@@ -14286,7 +14317,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:16" hidden="1">
       <c r="A195" s="23">
         <v>188</v>
       </c>
@@ -14300,7 +14331,7 @@
         <v>31</v>
       </c>
       <c r="E195" s="23" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F195" s="23">
         <v>3</v>
@@ -14327,7 +14358,7 @@
       </c>
       <c r="M195" s="28"/>
       <c r="N195" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O195" s="14" t="s">
         <v>139</v>
@@ -14337,7 +14368,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:16" hidden="1">
       <c r="A196" s="23">
         <v>189</v>
       </c>
@@ -14351,7 +14382,7 @@
         <v>31</v>
       </c>
       <c r="E196" s="23" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F196" s="23">
         <v>3</v>
@@ -14378,7 +14409,7 @@
       </c>
       <c r="M196" s="28"/>
       <c r="N196" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O196" s="14" t="s">
         <v>139</v>
@@ -14388,7 +14419,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:16" hidden="1">
       <c r="A197" s="23">
         <v>190</v>
       </c>
@@ -14402,7 +14433,7 @@
         <v>31</v>
       </c>
       <c r="E197" s="23" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F197" s="23">
         <v>3</v>
@@ -14429,7 +14460,7 @@
       </c>
       <c r="M197" s="28"/>
       <c r="N197" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O197" s="14" t="s">
         <v>139</v>
@@ -14439,7 +14470,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:16" hidden="1">
       <c r="A198" s="23">
         <v>191</v>
       </c>
@@ -14453,7 +14484,7 @@
         <v>31</v>
       </c>
       <c r="E198" s="23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F198" s="23">
         <v>3</v>
@@ -14480,7 +14511,7 @@
       </c>
       <c r="M198" s="28"/>
       <c r="N198" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O198" s="14" t="s">
         <v>139</v>
@@ -14490,7 +14521,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:16" hidden="1">
       <c r="A199" s="23">
         <v>192</v>
       </c>
@@ -14504,7 +14535,7 @@
         <v>31</v>
       </c>
       <c r="E199" s="23" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F199" s="23">
         <v>3</v>
@@ -14531,7 +14562,7 @@
       </c>
       <c r="M199" s="28"/>
       <c r="N199" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O199" s="14" t="s">
         <v>139</v>
@@ -14541,7 +14572,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:16" hidden="1">
       <c r="A200" s="23">
         <v>193</v>
       </c>
@@ -14555,7 +14586,7 @@
         <v>31</v>
       </c>
       <c r="E200" s="23" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F200" s="23">
         <v>2</v>
@@ -14582,7 +14613,7 @@
       </c>
       <c r="M200" s="28"/>
       <c r="N200" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O200" s="14" t="s">
         <v>139</v>
@@ -14592,7 +14623,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:16" hidden="1">
       <c r="A201" s="23">
         <v>194</v>
       </c>
@@ -14606,7 +14637,7 @@
         <v>31</v>
       </c>
       <c r="E201" s="23" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F201" s="23">
         <v>3</v>
@@ -14633,7 +14664,7 @@
       </c>
       <c r="M201" s="28"/>
       <c r="N201" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O201" s="14" t="s">
         <v>139</v>
@@ -14643,7 +14674,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:16" hidden="1">
       <c r="A202" s="23">
         <v>195</v>
       </c>
@@ -14657,7 +14688,7 @@
         <v>31</v>
       </c>
       <c r="E202" s="23" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F202" s="23">
         <v>3</v>
@@ -14684,7 +14715,7 @@
       </c>
       <c r="M202" s="28"/>
       <c r="N202" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O202" s="14" t="s">
         <v>139</v>
@@ -14694,7 +14725,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:16" hidden="1">
       <c r="A203" s="23">
         <v>196</v>
       </c>
@@ -14708,7 +14739,7 @@
         <v>31</v>
       </c>
       <c r="E203" s="23" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F203" s="23">
         <v>3</v>
@@ -14735,7 +14766,7 @@
       </c>
       <c r="M203" s="28"/>
       <c r="N203" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O203" s="14" t="s">
         <v>139</v>
@@ -14745,7 +14776,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:16" hidden="1">
       <c r="A204" s="23">
         <v>197</v>
       </c>
@@ -14759,7 +14790,7 @@
         <v>31</v>
       </c>
       <c r="E204" s="23" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F204" s="23">
         <v>3</v>
@@ -14786,7 +14817,7 @@
       </c>
       <c r="M204" s="28"/>
       <c r="N204" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O204" s="14" t="s">
         <v>139</v>
@@ -14796,7 +14827,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:16" hidden="1">
       <c r="A205" s="23">
         <v>198</v>
       </c>
@@ -14810,7 +14841,7 @@
         <v>31</v>
       </c>
       <c r="E205" s="23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F205" s="23">
         <v>3</v>
@@ -14837,7 +14868,7 @@
       </c>
       <c r="M205" s="28"/>
       <c r="N205" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O205" s="14" t="s">
         <v>139</v>
@@ -14847,7 +14878,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:16" hidden="1">
       <c r="A206" s="23">
         <v>199</v>
       </c>
@@ -14861,7 +14892,7 @@
         <v>31</v>
       </c>
       <c r="E206" s="23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F206" s="23">
         <v>3</v>
@@ -14888,7 +14919,7 @@
       </c>
       <c r="M206" s="28"/>
       <c r="N206" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O206" s="14" t="s">
         <v>139</v>
@@ -14898,7 +14929,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:16" hidden="1">
       <c r="A207" s="23">
         <v>200</v>
       </c>
@@ -14912,7 +14943,7 @@
         <v>31</v>
       </c>
       <c r="E207" s="23" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F207" s="23">
         <v>3</v>
@@ -14939,7 +14970,7 @@
       </c>
       <c r="M207" s="28"/>
       <c r="N207" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O207" s="14" t="s">
         <v>139</v>
@@ -14949,7 +14980,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:16" hidden="1">
       <c r="A208" s="23">
         <v>201</v>
       </c>
@@ -14963,7 +14994,7 @@
         <v>31</v>
       </c>
       <c r="E208" s="23" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F208" s="23">
         <v>3</v>
@@ -14990,7 +15021,7 @@
       </c>
       <c r="M208" s="28"/>
       <c r="N208" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O208" s="14" t="s">
         <v>139</v>
@@ -15000,7 +15031,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:16" hidden="1">
       <c r="A209" s="23">
         <v>202</v>
       </c>
@@ -15014,7 +15045,7 @@
         <v>31</v>
       </c>
       <c r="E209" s="23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F209" s="23">
         <v>3</v>
@@ -15041,7 +15072,7 @@
       </c>
       <c r="M209" s="28"/>
       <c r="N209" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O209" s="14" t="s">
         <v>139</v>
@@ -15051,7 +15082,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:16" hidden="1">
       <c r="A210" s="23">
         <v>203</v>
       </c>
@@ -15065,7 +15096,7 @@
         <v>31</v>
       </c>
       <c r="E210" s="23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F210" s="23">
         <v>3</v>
@@ -15092,7 +15123,7 @@
       </c>
       <c r="M210" s="28"/>
       <c r="N210" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O210" s="14" t="s">
         <v>139</v>
@@ -15102,7 +15133,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:16" hidden="1">
       <c r="A211" s="23">
         <v>204</v>
       </c>
@@ -15116,7 +15147,7 @@
         <v>31</v>
       </c>
       <c r="E211" s="23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F211" s="23">
         <v>3</v>
@@ -15143,7 +15174,7 @@
       </c>
       <c r="M211" s="28"/>
       <c r="N211" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O211" s="14" t="s">
         <v>139</v>
@@ -15153,7 +15184,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:16" hidden="1">
       <c r="A212" s="23">
         <v>205</v>
       </c>
@@ -15167,7 +15198,7 @@
         <v>31</v>
       </c>
       <c r="E212" s="23" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F212" s="23">
         <v>2</v>
@@ -15194,7 +15225,7 @@
       </c>
       <c r="M212" s="28"/>
       <c r="N212" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O212" s="14" t="s">
         <v>139</v>
@@ -15204,7 +15235,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:16" hidden="1">
       <c r="A213" s="23">
         <v>206</v>
       </c>
@@ -15255,7 +15286,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:16" hidden="1">
       <c r="A214" s="23">
         <v>207</v>
       </c>
@@ -15269,7 +15300,7 @@
         <v>28</v>
       </c>
       <c r="E214" s="23" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F214" s="23">
         <v>2</v>
@@ -15289,7 +15320,7 @@
         <v>⚠️ Missing Key</v>
       </c>
       <c r="K214" s="23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L214" s="23" t="s">
         <v>137</v>
@@ -15299,14 +15330,14 @@
         <v>34</v>
       </c>
       <c r="O214" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P214" s="14" t="str">
         <f t="shared" si="11"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:16" hidden="1">
       <c r="A215" s="23">
         <v>208</v>
       </c>
@@ -15346,10 +15377,10 @@
         <v>137</v>
       </c>
       <c r="M215" s="28" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N215" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O215" s="14" t="s">
         <v>139</v>
@@ -15359,7 +15390,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:16" hidden="1">
       <c r="A216" s="23">
         <v>209</v>
       </c>
@@ -15410,7 +15441,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:16" hidden="1">
       <c r="A217" s="23">
         <v>210</v>
       </c>
@@ -15450,7 +15481,7 @@
         <v>137</v>
       </c>
       <c r="M217" s="28" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N217" s="14" t="s">
         <v>35</v>
@@ -15463,7 +15494,7 @@
         <v>🟢 AVAILABLE</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:16" hidden="1">
       <c r="A218" s="23">
         <v>211</v>
       </c>
@@ -15503,7 +15534,7 @@
         <v>137</v>
       </c>
       <c r="M218" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N218" s="14" t="s">
         <v>34</v>
@@ -15516,7 +15547,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:16" hidden="1">
       <c r="A219" s="23">
         <v>212</v>
       </c>
@@ -15530,7 +15561,7 @@
         <v>28</v>
       </c>
       <c r="E219" s="23" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F219" s="23">
         <v>2</v>
@@ -15557,7 +15588,7 @@
       </c>
       <c r="M219" s="28"/>
       <c r="N219" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O219" s="14" t="s">
         <v>139</v>
@@ -15567,7 +15598,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16" hidden="1">
       <c r="A220" s="23">
         <v>213</v>
       </c>
@@ -15581,7 +15612,7 @@
         <v>31</v>
       </c>
       <c r="E220" s="23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F220" s="23">
         <v>2</v>
@@ -15608,7 +15639,7 @@
       </c>
       <c r="M220" s="28"/>
       <c r="N220" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O220" s="14" t="s">
         <v>188</v>
@@ -15618,7 +15649,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:16" hidden="1">
       <c r="A221" s="23">
         <v>214</v>
       </c>
@@ -15632,7 +15663,7 @@
         <v>31</v>
       </c>
       <c r="E221" s="23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F221" s="23">
         <v>2</v>
@@ -15659,7 +15690,7 @@
       </c>
       <c r="M221" s="28"/>
       <c r="N221" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O221" s="14" t="s">
         <v>188</v>
@@ -15669,7 +15700,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:16" hidden="1">
       <c r="A222" s="23">
         <v>215</v>
       </c>
@@ -15683,7 +15714,7 @@
         <v>31</v>
       </c>
       <c r="E222" s="23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F222" s="23">
         <v>2</v>
@@ -15710,7 +15741,7 @@
       </c>
       <c r="M222" s="28"/>
       <c r="N222" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O222" s="14" t="s">
         <v>188</v>
@@ -15720,7 +15751,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:16" hidden="1">
       <c r="A223" s="23">
         <v>216</v>
       </c>
@@ -15734,7 +15765,7 @@
         <v>31</v>
       </c>
       <c r="E223" s="23" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F223" s="23">
         <v>2</v>
@@ -15761,7 +15792,7 @@
       </c>
       <c r="M223" s="28"/>
       <c r="N223" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O223" s="14" t="s">
         <v>188</v>
@@ -15771,7 +15802,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:16" hidden="1">
       <c r="A224" s="23">
         <v>217</v>
       </c>
@@ -15785,7 +15816,7 @@
         <v>31</v>
       </c>
       <c r="E224" s="23" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F224" s="23">
         <v>2</v>
@@ -15812,7 +15843,7 @@
       </c>
       <c r="M224" s="28"/>
       <c r="N224" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O224" s="14" t="s">
         <v>139</v>
@@ -15822,7 +15853,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:16" hidden="1">
       <c r="A225" s="23">
         <v>218</v>
       </c>
@@ -15836,7 +15867,7 @@
         <v>31</v>
       </c>
       <c r="E225" s="23" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F225" s="23">
         <v>2</v>
@@ -15863,7 +15894,7 @@
       </c>
       <c r="M225" s="28"/>
       <c r="N225" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O225" s="14" t="s">
         <v>139</v>
@@ -15873,7 +15904,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:16" hidden="1">
       <c r="A226" s="23">
         <v>219</v>
       </c>
@@ -15887,7 +15918,7 @@
         <v>31</v>
       </c>
       <c r="E226" s="23" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F226" s="23">
         <v>3</v>
@@ -15914,7 +15945,7 @@
       </c>
       <c r="M226" s="28"/>
       <c r="N226" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O226" s="14" t="s">
         <v>139</v>
@@ -15924,7 +15955,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:16" hidden="1">
       <c r="A227" s="23">
         <v>220</v>
       </c>
@@ -15938,7 +15969,7 @@
         <v>31</v>
       </c>
       <c r="E227" s="23" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F227" s="23">
         <v>3</v>
@@ -15967,7 +15998,7 @@
         <v>177</v>
       </c>
       <c r="N227" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O227" s="14" t="s">
         <v>139</v>
@@ -15977,7 +16008,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:16" hidden="1">
       <c r="A228" s="23">
         <v>221</v>
       </c>
@@ -15991,7 +16022,7 @@
         <v>31</v>
       </c>
       <c r="E228" s="23" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F228" s="23">
         <v>2</v>
@@ -16020,7 +16051,7 @@
         <v>177</v>
       </c>
       <c r="N228" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O228" s="14" t="s">
         <v>139</v>
@@ -16030,7 +16061,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:16" hidden="1">
       <c r="A229" s="23">
         <v>222</v>
       </c>
@@ -16044,7 +16075,7 @@
         <v>31</v>
       </c>
       <c r="E229" s="23" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F229" s="23">
         <v>3</v>
@@ -16071,7 +16102,7 @@
       </c>
       <c r="M229" s="28"/>
       <c r="N229" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O229" s="14" t="s">
         <v>139</v>
@@ -16081,7 +16112,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:16" hidden="1">
       <c r="A230" s="23">
         <v>223</v>
       </c>
@@ -16095,7 +16126,7 @@
         <v>31</v>
       </c>
       <c r="E230" s="23" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F230" s="23">
         <v>3</v>
@@ -16122,7 +16153,7 @@
       </c>
       <c r="M230" s="28"/>
       <c r="N230" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O230" s="14" t="s">
         <v>139</v>
@@ -16132,7 +16163,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:16" hidden="1">
       <c r="A231" s="23">
         <v>224</v>
       </c>
@@ -16146,7 +16177,7 @@
         <v>31</v>
       </c>
       <c r="E231" s="23" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F231" s="23">
         <v>3</v>
@@ -16173,7 +16204,7 @@
       </c>
       <c r="M231" s="28"/>
       <c r="N231" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O231" s="14" t="s">
         <v>139</v>
@@ -16183,7 +16214,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:16" hidden="1">
       <c r="A232" s="23">
         <v>225</v>
       </c>
@@ -16197,7 +16228,7 @@
         <v>31</v>
       </c>
       <c r="E232" s="23" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F232" s="23">
         <v>3</v>
@@ -16224,7 +16255,7 @@
       </c>
       <c r="M232" s="28"/>
       <c r="N232" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O232" s="14" t="s">
         <v>139</v>
@@ -16234,7 +16265,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:16" hidden="1">
       <c r="A233" s="23">
         <v>226</v>
       </c>
@@ -16248,7 +16279,7 @@
         <v>31</v>
       </c>
       <c r="E233" s="23" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F233" s="23">
         <v>2</v>
@@ -16275,7 +16306,7 @@
       </c>
       <c r="M233" s="28"/>
       <c r="N233" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O233" s="14" t="s">
         <v>139</v>
@@ -16285,7 +16316,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:16" hidden="1">
       <c r="A234" s="23">
         <v>227</v>
       </c>
@@ -16299,7 +16330,7 @@
         <v>31</v>
       </c>
       <c r="E234" s="23" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F234" s="23">
         <v>3</v>
@@ -16326,7 +16357,7 @@
       </c>
       <c r="M234" s="28"/>
       <c r="N234" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O234" s="14" t="s">
         <v>139</v>
@@ -16336,7 +16367,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16" hidden="1">
       <c r="A235" s="23">
         <v>228</v>
       </c>
@@ -16350,7 +16381,7 @@
         <v>31</v>
       </c>
       <c r="E235" s="23" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F235" s="23">
         <v>2</v>
@@ -16377,7 +16408,7 @@
       </c>
       <c r="M235" s="28"/>
       <c r="N235" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O235" s="14" t="s">
         <v>139</v>
@@ -16387,7 +16418,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:16" hidden="1">
       <c r="A236" s="23">
         <v>229</v>
       </c>
@@ -16401,7 +16432,7 @@
         <v>31</v>
       </c>
       <c r="E236" s="23" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F236" s="23">
         <v>2</v>
@@ -16428,7 +16459,7 @@
       </c>
       <c r="M236" s="28"/>
       <c r="N236" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O236" s="14" t="s">
         <v>139</v>
@@ -16438,7 +16469,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16" hidden="1">
       <c r="A237" s="23">
         <v>230</v>
       </c>
@@ -16452,7 +16483,7 @@
         <v>31</v>
       </c>
       <c r="E237" s="23" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F237" s="23">
         <v>9</v>
@@ -16479,7 +16510,7 @@
       </c>
       <c r="M237" s="28"/>
       <c r="N237" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O237" s="14" t="s">
         <v>139</v>
@@ -16489,7 +16520,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:16" hidden="1">
       <c r="A238" s="23">
         <v>231</v>
       </c>
@@ -16503,7 +16534,7 @@
         <v>31</v>
       </c>
       <c r="E238" s="23" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F238" s="23">
         <v>4</v>
@@ -16530,7 +16561,7 @@
       </c>
       <c r="M238" s="28"/>
       <c r="N238" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O238" s="14" t="s">
         <v>139</v>
@@ -16540,7 +16571,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:16" hidden="1">
       <c r="A239" s="23">
         <v>232</v>
       </c>
@@ -16554,7 +16585,7 @@
         <v>28</v>
       </c>
       <c r="E239" s="23" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F239" s="23">
         <v>2</v>
@@ -16577,21 +16608,21 @@
         <v>70</v>
       </c>
       <c r="L239" s="23" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M239" s="28"/>
       <c r="N239" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O239" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P239" s="14" t="str">
         <f t="shared" si="11"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:16" hidden="1">
       <c r="A240" s="23">
         <v>233</v>
       </c>
@@ -16605,7 +16636,7 @@
         <v>28</v>
       </c>
       <c r="E240" s="23" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F240" s="23">
         <v>2</v>
@@ -16628,21 +16659,21 @@
         <v>70</v>
       </c>
       <c r="L240" s="23" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M240" s="28"/>
       <c r="N240" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O240" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P240" s="14" t="str">
         <f t="shared" si="11"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:16" hidden="1">
       <c r="A241" s="23">
         <v>234</v>
       </c>
@@ -16656,7 +16687,7 @@
         <v>28</v>
       </c>
       <c r="E241" s="23" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F241" s="23">
         <v>2</v>
@@ -16679,21 +16710,21 @@
         <v>70</v>
       </c>
       <c r="L241" s="23" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M241" s="28"/>
       <c r="N241" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O241" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P241" s="14" t="str">
         <f t="shared" si="11"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:16" hidden="1">
       <c r="A242" s="23">
         <v>235</v>
       </c>
@@ -16707,7 +16738,7 @@
         <v>28</v>
       </c>
       <c r="E242" s="23" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F242" s="23">
         <v>2</v>
@@ -16730,21 +16761,21 @@
         <v>70</v>
       </c>
       <c r="L242" s="23" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M242" s="28"/>
       <c r="N242" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O242" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P242" s="14" t="str">
         <f t="shared" si="11"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:16" hidden="1">
       <c r="A243" s="23">
         <v>236</v>
       </c>
@@ -16758,7 +16789,7 @@
         <v>28</v>
       </c>
       <c r="E243" s="23" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F243" s="23">
         <v>2</v>
@@ -16781,21 +16812,21 @@
         <v>70</v>
       </c>
       <c r="L243" s="23" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M243" s="28"/>
       <c r="N243" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O243" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P243" s="14" t="str">
         <f t="shared" si="11"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:16" hidden="1">
       <c r="A244" s="23">
         <v>237</v>
       </c>
@@ -16809,7 +16840,7 @@
         <v>28</v>
       </c>
       <c r="E244" s="23" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F244" s="23">
         <v>2</v>
@@ -16832,21 +16863,21 @@
         <v>70</v>
       </c>
       <c r="L244" s="23" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M244" s="28"/>
       <c r="N244" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O244" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P244" s="14" t="str">
         <f t="shared" si="11"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:16" hidden="1">
       <c r="A245" s="23">
         <v>238</v>
       </c>
@@ -16889,17 +16920,17 @@
         <v>195</v>
       </c>
       <c r="N245" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O245" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P245" s="14" t="str">
         <f t="shared" si="11"/>
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:16" hidden="1">
       <c r="A246" s="23">
         <v>239</v>
       </c>
@@ -16942,17 +16973,17 @@
         <v>192</v>
       </c>
       <c r="N246" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O246" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P246" s="14" t="str">
         <f t="shared" si="11"/>
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:16" hidden="1">
       <c r="A247" s="23">
         <v>240</v>
       </c>
@@ -16995,17 +17026,17 @@
         <v>204</v>
       </c>
       <c r="N247" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O247" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P247" s="14" t="str">
         <f t="shared" si="11"/>
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="248" spans="1:16" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:16" s="12" customFormat="1" hidden="1">
       <c r="A248" s="23">
         <v>241</v>
       </c>
@@ -17019,7 +17050,7 @@
         <v>28</v>
       </c>
       <c r="E248" s="23" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F248" s="23">
         <v>2</v>
@@ -17045,20 +17076,20 @@
         <v>137</v>
       </c>
       <c r="M248" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N248" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O248" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P248" s="14" t="str">
         <f t="shared" si="11"/>
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:16" hidden="1">
       <c r="A249" s="23">
         <v>242</v>
       </c>
@@ -17072,7 +17103,7 @@
         <v>28</v>
       </c>
       <c r="E249" s="23" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F249" s="23">
         <v>2</v>
@@ -17098,20 +17129,20 @@
         <v>137</v>
       </c>
       <c r="M249" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N249" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O249" s="14" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P249" s="14" t="str">
         <f t="shared" si="11"/>
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:16" hidden="1">
       <c r="A250" s="23">
         <v>243</v>
       </c>
@@ -17144,7 +17175,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:16" hidden="1">
       <c r="A251" s="23">
         <v>244</v>
       </c>
@@ -17158,7 +17189,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="23" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F251" s="23">
         <v>2</v>
@@ -17191,7 +17222,7 @@
         <v>🚨 REPLACE LOCK / KEY LOST</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:16" hidden="1">
       <c r="A252" s="23"/>
       <c r="B252" s="23"/>
       <c r="C252" s="24"/>
@@ -17215,7 +17246,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:16" hidden="1">
       <c r="A253" s="23"/>
       <c r="B253" s="23"/>
       <c r="C253" s="24"/>
@@ -17239,7 +17270,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:16" hidden="1">
       <c r="A254" s="23"/>
       <c r="B254" s="23"/>
       <c r="C254" s="24"/>
@@ -17263,7 +17294,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:16" hidden="1">
       <c r="A255" s="23"/>
       <c r="B255" s="23"/>
       <c r="C255" s="24"/>
@@ -17287,7 +17318,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:16" hidden="1">
       <c r="A256" s="23"/>
       <c r="B256" s="23"/>
       <c r="C256" s="24"/>
@@ -17311,7 +17342,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:16" hidden="1">
       <c r="A257" s="23"/>
       <c r="B257" s="23"/>
       <c r="C257" s="24"/>
@@ -17335,7 +17366,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16">
       <c r="A258" s="23"/>
       <c r="B258" s="23"/>
       <c r="C258" s="24"/>
@@ -17353,7 +17384,7 @@
       <c r="O258" s="14"/>
       <c r="P258" s="14"/>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16">
       <c r="A259" s="23"/>
       <c r="B259" s="23"/>
       <c r="C259" s="24"/>
@@ -17371,7 +17402,7 @@
       <c r="O259" s="14"/>
       <c r="P259" s="14"/>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:16">
       <c r="A260" s="23"/>
       <c r="B260" s="23"/>
       <c r="C260" s="24"/>
@@ -17389,7 +17420,7 @@
       <c r="O260" s="14"/>
       <c r="P260" s="14"/>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:16">
       <c r="A261" s="23"/>
       <c r="B261" s="23"/>
       <c r="C261" s="24"/>
@@ -17407,7 +17438,7 @@
       <c r="O261" s="14"/>
       <c r="P261" s="14"/>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:16">
       <c r="A262" s="23"/>
       <c r="B262" s="23"/>
       <c r="C262" s="24"/>
@@ -17425,7 +17456,7 @@
       <c r="O262" s="14"/>
       <c r="P262" s="14"/>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16">
       <c r="A263" s="23"/>
       <c r="B263" s="23"/>
       <c r="C263" s="24"/>
@@ -17443,7 +17474,7 @@
       <c r="O263" s="14"/>
       <c r="P263" s="14"/>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16">
       <c r="A264" s="23"/>
       <c r="B264" s="23"/>
       <c r="C264" s="24"/>
@@ -17461,7 +17492,7 @@
       <c r="O264" s="14"/>
       <c r="P264" s="14"/>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:16">
       <c r="A265" s="23"/>
       <c r="B265" s="23"/>
       <c r="C265" s="24"/>
@@ -17479,7 +17510,7 @@
       <c r="O265" s="14"/>
       <c r="P265" s="14"/>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:16">
       <c r="A266" s="23"/>
       <c r="B266" s="23"/>
       <c r="C266" s="24"/>
@@ -17497,7 +17528,7 @@
       <c r="O266" s="14"/>
       <c r="P266" s="14"/>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:16">
       <c r="A267" s="23"/>
       <c r="B267" s="23"/>
       <c r="C267" s="24"/>
@@ -17530,34 +17561,34 @@
     <mergeCell ref="K6:M6"/>
   </mergeCells>
   <conditionalFormatting sqref="A8:P267">
-    <cfRule type="expression" dxfId="12" priority="17">
+    <cfRule type="expression" dxfId="26" priority="17">
       <formula>AND($C$5&lt;&gt;"", ISNUMBER(SEARCH($C$5, $A8&amp;" "&amp;$B8&amp;" "&amp;$C8&amp;" "&amp;$D8&amp;" "&amp;$E8&amp;" "&amp;$F8&amp;" "&amp;$G8&amp;" "&amp;$H8&amp;" "&amp;$I8&amp;" "&amp;$J8&amp;" "&amp;$K8&amp;" "&amp;$L8&amp;" "&amp;$M8&amp;" "&amp;$N8&amp;" "&amp;$O8&amp;" "&amp;$P8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I8:I267">
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="10" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N8:N267">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="11" operator="equal">
       <formula>"Occupied"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="12" operator="equal">
       <formula>"Vacant"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="13" operator="equal">
       <formula>"Under Audit"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P8:P267">
-    <cfRule type="expression" dxfId="7" priority="14">
+    <cfRule type="expression" dxfId="21" priority="14">
       <formula>NOT(ISERROR(SEARCH("REPLACE",P8)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="15">
+    <cfRule type="expression" dxfId="20" priority="15">
       <formula>NOT(ISERROR(SEARCH("AUDIT",P8)))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="16">
+    <cfRule type="expression" dxfId="19" priority="16">
       <formula>NOT(ISERROR(SEARCH("AVAILABLE",P8)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17582,22 +17613,22 @@
     <tabColor rgb="FFC62828"/>
   </sheetPr>
   <dimension ref="A2:L27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" customWidth="1"/>
-    <col min="2" max="2" width="18.7265625" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" customWidth="1"/>
-    <col min="5" max="5" width="28.7265625" customWidth="1"/>
-    <col min="6" max="6" width="34.7265625" customWidth="1"/>
-    <col min="7" max="7" width="40.7265625" customWidth="1"/>
-    <col min="8" max="8" width="24.7265625" customWidth="1"/>
-    <col min="9" max="10" width="14.7265625" customWidth="1"/>
-    <col min="11" max="11" width="16.7265625" customWidth="1"/>
-    <col min="12" max="12" width="20.7265625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="34.7109375" customWidth="1"/>
+    <col min="7" max="7" width="40.7109375" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="27.95" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -17621,39 +17652,39 @@
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
     </row>
-    <row r="4" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="69" t="s">
-        <v>321</v>
-      </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-    </row>
-    <row r="5" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="66" t="s">
-        <v>322</v>
-      </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="24.95" customHeight="1">
+      <c r="A4" s="40" t="s">
+        <v>323</v>
+      </c>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+    </row>
+    <row r="5" spans="1:12" ht="18" customHeight="1">
+      <c r="A5" s="54" t="s">
+        <v>324</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" s="15" t="s">
         <v>83</v>
       </c>
@@ -17670,13 +17701,13 @@
         <v>124</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>88</v>
@@ -17685,13 +17716,13 @@
         <v>89</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="23" t="s">
         <v>90</v>
       </c>
@@ -17711,10 +17742,10 @@
         <v>188</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I8" s="23" t="s">
         <v>108</v>
@@ -17723,13 +17754,13 @@
         <v>109</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" s="23" t="s">
         <v>96</v>
       </c>
@@ -17749,10 +17780,10 @@
         <v>188</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I9" s="23" t="s">
         <v>108</v>
@@ -17761,13 +17792,13 @@
         <v>109</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="23" t="s">
         <v>98</v>
       </c>
@@ -17787,10 +17818,10 @@
         <v>188</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I10" s="23" t="s">
         <v>108</v>
@@ -17799,13 +17830,13 @@
         <v>109</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" s="23" t="s">
         <v>101</v>
       </c>
@@ -17825,10 +17856,10 @@
         <v>198</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I11" s="23" t="s">
         <v>94</v>
@@ -17837,13 +17868,13 @@
         <v>95</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="23" t="s">
         <v>104</v>
       </c>
@@ -17863,10 +17894,10 @@
         <v>188</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>108</v>
@@ -17875,13 +17906,13 @@
         <v>109</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="23" t="s">
         <v>110</v>
       </c>
@@ -17901,10 +17932,10 @@
         <v>201</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I13" s="23" t="s">
         <v>108</v>
@@ -17913,13 +17944,13 @@
         <v>109</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="23" t="s">
         <v>114</v>
       </c>
@@ -17939,10 +17970,10 @@
         <v>188</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I14" s="23" t="s">
         <v>108</v>
@@ -17951,15 +17982,15 @@
         <v>109</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="23" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>49</v>
@@ -17977,10 +18008,10 @@
         <v>188</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I15" s="23" t="s">
         <v>108</v>
@@ -17989,15 +18020,15 @@
         <v>109</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="23" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>49</v>
@@ -18015,10 +18046,10 @@
         <v>188</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I16" s="23" t="s">
         <v>108</v>
@@ -18027,15 +18058,15 @@
         <v>109</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="23" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>59</v>
@@ -18053,10 +18084,10 @@
         <v>234</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I17" s="23" t="s">
         <v>108</v>
@@ -18065,15 +18096,15 @@
         <v>109</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="23" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B18" s="23" t="s">
         <v>63</v>
@@ -18088,13 +18119,13 @@
         <v>63</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I18" s="23" t="s">
         <v>108</v>
@@ -18103,15 +18134,15 @@
         <v>109</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="23" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B19" s="23" t="s">
         <v>63</v>
@@ -18126,13 +18157,13 @@
         <v>63</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I19" s="23" t="s">
         <v>108</v>
@@ -18141,15 +18172,15 @@
         <v>109</v>
       </c>
       <c r="K19" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="23" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>43</v>
@@ -18164,13 +18195,13 @@
         <v>103</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I20" s="23" t="s">
         <v>94</v>
@@ -18179,15 +18210,15 @@
         <v>95</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="23" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>54</v>
@@ -18199,16 +18230,16 @@
         <v>31</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I21" s="23" t="s">
         <v>108</v>
@@ -18217,15 +18248,15 @@
         <v>109</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="23" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>45</v>
@@ -18237,16 +18268,16 @@
         <v>31</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F22" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I22" s="23" t="s">
         <v>108</v>
@@ -18255,15 +18286,15 @@
         <v>109</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="23" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B23" s="23" t="s">
         <v>54</v>
@@ -18275,16 +18306,16 @@
         <v>31</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I23" s="23" t="s">
         <v>108</v>
@@ -18293,15 +18324,15 @@
         <v>109</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="23" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B24" s="23" t="s">
         <v>54</v>
@@ -18313,16 +18344,16 @@
         <v>31</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F24" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I24" s="23" t="s">
         <v>108</v>
@@ -18331,15 +18362,15 @@
         <v>109</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="29.1" customHeight="1">
       <c r="A25" s="23" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B25" s="23" t="s">
         <v>45</v>
@@ -18354,13 +18385,13 @@
         <v>92</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I25" s="23" t="s">
         <v>94</v>
@@ -18369,15 +18400,15 @@
         <v>95</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="29.1" customHeight="1">
       <c r="A26" s="23" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>45</v>
@@ -18392,13 +18423,13 @@
         <v>92</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I26" s="23" t="s">
         <v>94</v>
@@ -18407,15 +18438,15 @@
         <v>95</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="29.1" customHeight="1">
       <c r="A27" s="23" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>47</v>
@@ -18430,13 +18461,13 @@
         <v>100</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I27" s="23" t="s">
         <v>94</v>
@@ -18445,10 +18476,10 @@
         <v>95</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -18457,21 +18488,21 @@
     <mergeCell ref="A4:L4"/>
   </mergeCells>
   <conditionalFormatting sqref="I8:I27">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"High"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"Medium"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K8:K27">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"Pending"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
       <formula>"Resolved"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18495,17 +18526,17 @@
     <tabColor rgb="FF1565C0"/>
   </sheetPr>
   <dimension ref="B2:N23"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="4.7265625" customWidth="1"/>
-    <col min="2" max="2" width="24.7265625" customWidth="1"/>
-    <col min="3" max="3" width="14.7265625" customWidth="1"/>
-    <col min="4" max="8" width="13.7265625" customWidth="1"/>
-    <col min="9" max="9" width="15.7265625" customWidth="1"/>
-    <col min="10" max="13" width="14.7265625" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="8" width="13.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="13" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:14" ht="27.95" customHeight="1">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -18530,78 +18561,78 @@
       <c r="M2" s="15"/>
       <c r="N2" s="15"/>
     </row>
-    <row r="4" spans="2:14" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="69" t="s">
-        <v>367</v>
-      </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-    </row>
-    <row r="5" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="66" t="s">
-        <v>368</v>
-      </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-    </row>
-    <row r="7" spans="2:14" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="46" t="s">
+    <row r="4" spans="2:14" ht="24.95" customHeight="1">
+      <c r="B4" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="C7" s="47"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="48"/>
-    </row>
-    <row r="8" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+    </row>
+    <row r="5" spans="2:14" ht="18" customHeight="1">
+      <c r="B5" s="54" t="s">
+        <v>370</v>
+      </c>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+    </row>
+    <row r="7" spans="2:14" ht="21.95" customHeight="1">
+      <c r="B7" s="62" t="s">
+        <v>371</v>
+      </c>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
+      <c r="N7" s="71"/>
+    </row>
+    <row r="8" spans="2:14" ht="24" customHeight="1">
       <c r="B8" s="16" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>34</v>
@@ -18610,10 +18641,10 @@
         <v>35</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>127</v>
@@ -18622,7 +18653,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" ht="18" customHeight="1">
       <c r="B9" s="17" t="s">
         <v>39</v>
       </c>
@@ -18675,7 +18706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" ht="18" customHeight="1">
       <c r="B10" s="17" t="s">
         <v>41</v>
       </c>
@@ -18728,7 +18759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" ht="18" customHeight="1">
       <c r="B11" s="17" t="s">
         <v>43</v>
       </c>
@@ -18781,7 +18812,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" ht="18" customHeight="1">
       <c r="B12" s="17" t="s">
         <v>45</v>
       </c>
@@ -18834,7 +18865,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" ht="18" customHeight="1">
       <c r="B13" s="17" t="s">
         <v>47</v>
       </c>
@@ -18887,7 +18918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" ht="18" customHeight="1">
       <c r="B14" s="17" t="s">
         <v>49</v>
       </c>
@@ -18940,7 +18971,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" ht="18" customHeight="1">
       <c r="B15" s="17" t="s">
         <v>51</v>
       </c>
@@ -18993,7 +19024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" ht="18" customHeight="1">
       <c r="B16" s="17" t="s">
         <v>52</v>
       </c>
@@ -19046,7 +19077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" ht="18" customHeight="1">
       <c r="B17" s="17" t="s">
         <v>54</v>
       </c>
@@ -19099,7 +19130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" ht="18" customHeight="1">
       <c r="B18" s="17" t="s">
         <v>59</v>
       </c>
@@ -19152,7 +19183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" ht="18" customHeight="1">
       <c r="B19" s="17" t="s">
         <v>63</v>
       </c>
@@ -19205,7 +19236,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" ht="18" customHeight="1">
       <c r="B20" s="17" t="s">
         <v>66</v>
       </c>
@@ -19258,7 +19289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" ht="18" customHeight="1">
       <c r="B21" s="17" t="s">
         <v>69</v>
       </c>
@@ -19311,7 +19342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" ht="18" customHeight="1">
       <c r="B22" s="17" t="s">
         <v>73</v>
       </c>
@@ -19364,9 +19395,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:14" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" ht="20.100000000000001" customHeight="1">
       <c r="B23" s="19" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C23" s="20">
         <f t="shared" ref="C23:N23" si="0">SUM(C9:C22)</f>
@@ -19440,22 +19471,22 @@
     <tabColor rgb="FF455A64"/>
   </sheetPr>
   <dimension ref="A2:K19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="24.7265625" customWidth="1"/>
-    <col min="2" max="2" width="3.7265625" customWidth="1"/>
-    <col min="3" max="3" width="18.7265625" customWidth="1"/>
-    <col min="4" max="4" width="3.7265625" customWidth="1"/>
-    <col min="5" max="5" width="24.7265625" customWidth="1"/>
-    <col min="6" max="6" width="3.7265625" customWidth="1"/>
-    <col min="7" max="7" width="20.7265625" customWidth="1"/>
-    <col min="8" max="8" width="3.7265625" customWidth="1"/>
-    <col min="9" max="9" width="18.7265625" customWidth="1"/>
-    <col min="10" max="10" width="3.7265625" customWidth="1"/>
-    <col min="11" max="11" width="20.7265625" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="3.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="3.7109375" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="10" max="10" width="3.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="27.95" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -19478,47 +19509,47 @@
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
     </row>
-    <row r="4" spans="1:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="69" t="s">
-        <v>379</v>
-      </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-    </row>
-    <row r="5" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="24.95" customHeight="1">
+      <c r="A4" s="40" t="s">
+        <v>381</v>
+      </c>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.95" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.95" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>39</v>
       </c>
@@ -19540,10 +19571,10 @@
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="4" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.95" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>41</v>
       </c>
@@ -19565,10 +19596,10 @@
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="4" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.95" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>43</v>
       </c>
@@ -19578,22 +19609,22 @@
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.95" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>45</v>
       </c>
@@ -19614,7 +19645,7 @@
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
     </row>
-    <row r="10" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="15.95" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>47</v>
       </c>
@@ -19624,7 +19655,7 @@
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -19633,7 +19664,7 @@
       <c r="J10" s="15"/>
       <c r="K10" s="15"/>
     </row>
-    <row r="11" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="15.95" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>49</v>
       </c>
@@ -19648,7 +19679,7 @@
       <c r="J11" s="15"/>
       <c r="K11" s="15"/>
     </row>
-    <row r="12" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="15.95" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>51</v>
       </c>
@@ -19663,7 +19694,7 @@
       <c r="J12" s="15"/>
       <c r="K12" s="15"/>
     </row>
-    <row r="13" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="15.95" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>52</v>
       </c>
@@ -19678,7 +19709,7 @@
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
     </row>
-    <row r="14" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="15.95" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>54</v>
       </c>
@@ -19693,7 +19724,7 @@
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
     </row>
-    <row r="15" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15.95" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>59</v>
       </c>
@@ -19708,7 +19739,7 @@
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
     </row>
-    <row r="16" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="15.95" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>63</v>
       </c>
@@ -19723,17 +19754,17 @@
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
     </row>
-    <row r="17" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" ht="15.95" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" ht="15.95" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" ht="15.95" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>73</v>
       </c>

--- a/Locker/Keys Lock Tracker - 2026 1.xlsx
+++ b/Locker/Keys Lock Tracker - 2026 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cbre-my.sharepoint.com/personal/satyabrata_mohanty1_cbre_com/Documents/Desktop/Trackers/Locker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="342" documentId="11_F56D8C5A66DACF4247F893C0199D457268BC86FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0669E165-B7FC-433A-91B0-D711E43EEF81}"/>
+  <xr:revisionPtr revIDLastSave="434" documentId="11_F56D8C5A66DACF4247F893C0199D457268BC86FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BF8A4FE-C257-420E-8D6F-2E6E38366AE8}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11280" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2390" uniqueCount="394">
   <si>
     <t>📊 Executive Dashboard</t>
   </si>
@@ -831,6 +831,9 @@
     <t>MR - 101</t>
   </si>
   <si>
+    <t>Box No-15</t>
+  </si>
+  <si>
     <t>Common Asset</t>
   </si>
   <si>
@@ -844,6 +847,9 @@
   </si>
   <si>
     <t>MR - 106</t>
+  </si>
+  <si>
+    <t>Box NO-15</t>
   </si>
   <si>
     <t>MR - 107</t>
@@ -2543,7 +2549,7 @@
   <autoFilter ref="A7:P257" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="705"/>
+        <filter val="280"/>
         <filter val="(NonBlanks)"/>
       </filters>
     </filterColumn>
@@ -2988,7 +2994,7 @@
     <row r="8" spans="2:16" ht="27.95" customHeight="1">
       <c r="B8" s="65">
         <f>COUNTA(Table_Tracker[Lock No.])</f>
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C8" s="69"/>
       <c r="D8" s="69"/>
@@ -3009,7 +3015,7 @@
       <c r="M8" s="15"/>
       <c r="N8" s="61">
         <f>COUNTIF(Table_Tracker[Lock Status], "Common Asset")</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O8" s="69"/>
       <c r="P8" s="69"/>
@@ -3067,14 +3073,14 @@
     <row r="12" spans="2:16" ht="27.95" customHeight="1">
       <c r="B12" s="55">
         <f>SUM(Table_Tracker[Total Keys])</f>
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C12" s="69"/>
       <c r="D12" s="69"/>
       <c r="E12" s="15"/>
       <c r="F12" s="50">
         <f>SUM(Table_Tracker[Spare Keys (BMS)])</f>
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="G12" s="69"/>
       <c r="H12" s="69"/>
@@ -3088,7 +3094,7 @@
       <c r="M12" s="15"/>
       <c r="N12" s="52">
         <f>SUM(Table_Tracker[Missing Keys])</f>
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O12" s="69"/>
       <c r="P12" s="69"/>
@@ -3275,7 +3281,7 @@
       </c>
       <c r="K18" s="5">
         <f>COUNTIF(Table_Tracker[Lock Type], "Cupboard")</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L18" s="5">
         <f>COUNTIFS(Table_Tracker[Lock Type], "Cupboard", Table_Tracker[Lock Status], "Occupied")</f>
@@ -3287,7 +3293,7 @@
       </c>
       <c r="N18" s="5">
         <f>SUMIFS(Table_Tracker[Spare Keys (BMS)], Table_Tracker[Lock Type], "Cupboard")</f>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O18" s="5">
         <f>SUMIFS(Table_Tracker[Issued Keys], Table_Tracker[Lock Type], "Cupboard")</f>
@@ -3304,7 +3310,7 @@
       </c>
       <c r="C19" s="18">
         <f>COUNTIF(Table_Tracker[Zone], B19)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D19" s="18">
         <f>COUNTIFS(Table_Tracker[Zone], B19, Table_Tracker[Lock Type], "Planter")</f>
@@ -3312,7 +3318,7 @@
       </c>
       <c r="E19" s="18">
         <f>COUNTIFS(Table_Tracker[Zone], B19, Table_Tracker[Lock Type], "Cupboard")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F19" s="18">
         <f>COUNTIFS(Table_Tracker[Zone], B19, Table_Tracker[Lock Type], "Locker")</f>
@@ -3344,7 +3350,7 @@
       </c>
       <c r="N19" s="5">
         <f>SUMIFS(Table_Tracker[Spare Keys (BMS)], Table_Tracker[Lock Type], "Door")</f>
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O19" s="5">
         <f>SUMIFS(Table_Tracker[Issued Keys], Table_Tracker[Lock Type], "Door")</f>
@@ -3352,7 +3358,7 @@
       </c>
       <c r="P19" s="5">
         <f>SUMIFS(Table_Tracker[Missing Keys], Table_Tracker[Lock Type], "Door")</f>
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="2:16" ht="18" customHeight="1">
@@ -3401,7 +3407,7 @@
       </c>
       <c r="N20" s="5">
         <f>SUMIFS(Table_Tracker[Spare Keys (BMS)], Table_Tracker[Lock Type], "Locker")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O20" s="5">
         <f>SUMIFS(Table_Tracker[Issued Keys], Table_Tracker[Lock Type], "Locker")</f>
@@ -3409,7 +3415,7 @@
       </c>
       <c r="P20" s="5">
         <f>SUMIFS(Table_Tracker[Missing Keys], Table_Tracker[Lock Type], "Locker")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="2:16" ht="18" customHeight="1">
@@ -3503,7 +3509,7 @@
       </c>
       <c r="K22" s="7">
         <f t="shared" ref="K22:P22" si="0">SUM(K17:K21)</f>
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L22" s="7">
         <f t="shared" si="0"/>
@@ -3515,7 +3521,7 @@
       </c>
       <c r="N22" s="7">
         <f t="shared" si="0"/>
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O22" s="7">
         <f t="shared" si="0"/>
@@ -3523,7 +3529,7 @@
       </c>
       <c r="P22" s="7">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="2:16" ht="18" customHeight="1">
@@ -3890,7 +3896,7 @@
       </c>
       <c r="C31" s="20">
         <f t="shared" ref="C31:H31" si="1">SUM(C17:C30)</f>
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D31" s="20">
         <f t="shared" si="1"/>
@@ -3898,7 +3904,7 @@
       </c>
       <c r="E31" s="20">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F31" s="20">
         <f t="shared" si="1"/>
@@ -13237,7 +13243,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="174" spans="1:16">
+    <row r="174" spans="1:16" hidden="1">
       <c r="A174" s="23">
         <v>167</v>
       </c>
@@ -13257,18 +13263,18 @@
         <v>2</v>
       </c>
       <c r="G174" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H174" s="23">
         <v>0</v>
       </c>
       <c r="I174" s="23">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J174" s="23" t="str">
         <f t="shared" si="7"/>
-        <v>⚠️ Missing Key</v>
+        <v>🔒 In Custody</v>
       </c>
       <c r="K174" s="23"/>
       <c r="L174" s="23" t="s">
@@ -13285,7 +13291,7 @@
       </c>
       <c r="P174" s="14" t="str">
         <f t="shared" si="8"/>
-        <v>🚨 REPLACE LOCK / KEY LOST</v>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="175" spans="1:16" hidden="1">
@@ -13484,7 +13490,9 @@
       <c r="L178" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="M178" s="28"/>
+      <c r="M178" s="28" t="s">
+        <v>248</v>
+      </c>
       <c r="N178" s="14" t="s">
         <v>34</v>
       </c>
@@ -13846,9 +13854,11 @@
       <c r="L185" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="M185" s="28"/>
+      <c r="M185" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N185" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O185" s="14" t="s">
         <v>139</v>
@@ -13872,7 +13882,7 @@
         <v>31</v>
       </c>
       <c r="E186" s="23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F186" s="23">
         <v>3</v>
@@ -13897,9 +13907,11 @@
       <c r="L186" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="M186" s="28"/>
+      <c r="M186" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N186" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O186" s="14" t="s">
         <v>139</v>
@@ -13923,7 +13935,7 @@
         <v>31</v>
       </c>
       <c r="E187" s="23" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F187" s="23">
         <v>3</v>
@@ -13948,9 +13960,11 @@
       <c r="L187" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="M187" s="28"/>
+      <c r="M187" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N187" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O187" s="14" t="s">
         <v>139</v>
@@ -13974,7 +13988,7 @@
         <v>31</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F188" s="23">
         <v>3</v>
@@ -13999,9 +14013,11 @@
       <c r="L188" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M188" s="28"/>
+      <c r="M188" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N188" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O188" s="14" t="s">
         <v>139</v>
@@ -14025,7 +14041,7 @@
         <v>31</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F189" s="23">
         <v>3</v>
@@ -14050,9 +14066,11 @@
       <c r="L189" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M189" s="28"/>
+      <c r="M189" s="28" t="s">
+        <v>269</v>
+      </c>
       <c r="N189" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O189" s="14" t="s">
         <v>139</v>
@@ -14076,7 +14094,7 @@
         <v>31</v>
       </c>
       <c r="E190" s="23" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F190" s="23">
         <v>3</v>
@@ -14101,9 +14119,11 @@
       <c r="L190" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M190" s="28"/>
+      <c r="M190" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N190" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O190" s="14" t="s">
         <v>139</v>
@@ -14127,7 +14147,7 @@
         <v>31</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F191" s="23">
         <v>3</v>
@@ -14152,9 +14172,11 @@
       <c r="L191" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M191" s="28"/>
+      <c r="M191" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N191" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O191" s="14" t="s">
         <v>139</v>
@@ -14178,7 +14200,7 @@
         <v>31</v>
       </c>
       <c r="E192" s="23" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F192" s="23">
         <v>3</v>
@@ -14203,9 +14225,11 @@
       <c r="L192" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M192" s="28"/>
+      <c r="M192" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N192" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O192" s="14" t="s">
         <v>139</v>
@@ -14229,7 +14253,7 @@
         <v>31</v>
       </c>
       <c r="E193" s="23" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F193" s="23">
         <v>3</v>
@@ -14254,9 +14278,11 @@
       <c r="L193" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M193" s="28"/>
+      <c r="M193" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N193" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O193" s="14" t="s">
         <v>139</v>
@@ -14280,7 +14306,7 @@
         <v>31</v>
       </c>
       <c r="E194" s="23" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F194" s="23">
         <v>3</v>
@@ -14305,9 +14331,11 @@
       <c r="L194" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M194" s="28"/>
+      <c r="M194" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N194" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O194" s="14" t="s">
         <v>139</v>
@@ -14331,7 +14359,7 @@
         <v>31</v>
       </c>
       <c r="E195" s="23" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F195" s="23">
         <v>3</v>
@@ -14356,9 +14384,11 @@
       <c r="L195" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M195" s="28"/>
+      <c r="M195" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N195" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O195" s="14" t="s">
         <v>139</v>
@@ -14382,7 +14412,7 @@
         <v>31</v>
       </c>
       <c r="E196" s="23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F196" s="23">
         <v>3</v>
@@ -14407,9 +14437,11 @@
       <c r="L196" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M196" s="28"/>
+      <c r="M196" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N196" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O196" s="14" t="s">
         <v>139</v>
@@ -14433,7 +14465,7 @@
         <v>31</v>
       </c>
       <c r="E197" s="23" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F197" s="23">
         <v>3</v>
@@ -14458,9 +14490,11 @@
       <c r="L197" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M197" s="28"/>
+      <c r="M197" s="28" t="s">
+        <v>269</v>
+      </c>
       <c r="N197" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O197" s="14" t="s">
         <v>139</v>
@@ -14484,7 +14518,7 @@
         <v>31</v>
       </c>
       <c r="E198" s="23" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F198" s="23">
         <v>3</v>
@@ -14509,9 +14543,11 @@
       <c r="L198" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M198" s="28"/>
+      <c r="M198" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N198" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O198" s="14" t="s">
         <v>139</v>
@@ -14535,7 +14571,7 @@
         <v>31</v>
       </c>
       <c r="E199" s="23" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F199" s="23">
         <v>3</v>
@@ -14560,9 +14596,11 @@
       <c r="L199" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M199" s="28"/>
+      <c r="M199" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N199" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O199" s="14" t="s">
         <v>139</v>
@@ -14586,7 +14624,7 @@
         <v>31</v>
       </c>
       <c r="E200" s="23" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F200" s="23">
         <v>2</v>
@@ -14611,9 +14649,11 @@
       <c r="L200" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M200" s="28"/>
+      <c r="M200" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N200" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O200" s="14" t="s">
         <v>139</v>
@@ -14637,7 +14677,7 @@
         <v>31</v>
       </c>
       <c r="E201" s="23" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F201" s="23">
         <v>3</v>
@@ -14662,9 +14702,11 @@
       <c r="L201" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M201" s="28"/>
+      <c r="M201" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N201" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O201" s="14" t="s">
         <v>139</v>
@@ -14688,7 +14730,7 @@
         <v>31</v>
       </c>
       <c r="E202" s="23" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F202" s="23">
         <v>3</v>
@@ -14713,9 +14755,11 @@
       <c r="L202" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M202" s="28"/>
+      <c r="M202" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N202" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O202" s="14" t="s">
         <v>139</v>
@@ -14739,7 +14783,7 @@
         <v>31</v>
       </c>
       <c r="E203" s="23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F203" s="23">
         <v>3</v>
@@ -14764,9 +14808,11 @@
       <c r="L203" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M203" s="28"/>
+      <c r="M203" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N203" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O203" s="14" t="s">
         <v>139</v>
@@ -14790,7 +14836,7 @@
         <v>31</v>
       </c>
       <c r="E204" s="23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F204" s="23">
         <v>3</v>
@@ -14815,9 +14861,11 @@
       <c r="L204" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M204" s="28"/>
+      <c r="M204" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N204" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O204" s="14" t="s">
         <v>139</v>
@@ -14841,7 +14889,7 @@
         <v>31</v>
       </c>
       <c r="E205" s="23" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F205" s="23">
         <v>3</v>
@@ -14866,9 +14914,11 @@
       <c r="L205" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M205" s="28"/>
+      <c r="M205" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N205" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O205" s="14" t="s">
         <v>139</v>
@@ -14892,7 +14942,7 @@
         <v>31</v>
       </c>
       <c r="E206" s="23" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F206" s="23">
         <v>3</v>
@@ -14917,9 +14967,11 @@
       <c r="L206" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M206" s="28"/>
+      <c r="M206" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N206" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O206" s="14" t="s">
         <v>139</v>
@@ -14943,24 +14995,24 @@
         <v>31</v>
       </c>
       <c r="E207" s="23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F207" s="23">
         <v>3</v>
       </c>
       <c r="G207" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H207" s="23">
         <v>0</v>
       </c>
       <c r="I207" s="23">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J207" s="23" t="str">
         <f t="shared" si="10"/>
-        <v>⚠️ Missing Key</v>
+        <v>🔒 In Custody</v>
       </c>
       <c r="K207" s="23" t="s">
         <v>139</v>
@@ -14968,16 +15020,18 @@
       <c r="L207" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M207" s="28"/>
+      <c r="M207" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N207" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O207" s="14" t="s">
         <v>139</v>
       </c>
       <c r="P207" s="14" t="str">
         <f t="shared" si="11"/>
-        <v>🚨 REPLACE LOCK / KEY LOST</v>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="208" spans="1:16" hidden="1">
@@ -14994,7 +15048,7 @@
         <v>31</v>
       </c>
       <c r="E208" s="23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F208" s="23">
         <v>3</v>
@@ -15019,9 +15073,11 @@
       <c r="L208" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M208" s="28"/>
+      <c r="M208" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N208" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O208" s="14" t="s">
         <v>139</v>
@@ -15045,7 +15101,7 @@
         <v>31</v>
       </c>
       <c r="E209" s="23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F209" s="23">
         <v>3</v>
@@ -15070,9 +15126,11 @@
       <c r="L209" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M209" s="28"/>
+      <c r="M209" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N209" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O209" s="14" t="s">
         <v>139</v>
@@ -15096,7 +15154,7 @@
         <v>31</v>
       </c>
       <c r="E210" s="23" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F210" s="23">
         <v>3</v>
@@ -15121,9 +15179,11 @@
       <c r="L210" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M210" s="28"/>
+      <c r="M210" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N210" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O210" s="14" t="s">
         <v>139</v>
@@ -15147,7 +15207,7 @@
         <v>31</v>
       </c>
       <c r="E211" s="23" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F211" s="23">
         <v>3</v>
@@ -15172,9 +15232,11 @@
       <c r="L211" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M211" s="28"/>
+      <c r="M211" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N211" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O211" s="14" t="s">
         <v>139</v>
@@ -15198,7 +15260,7 @@
         <v>31</v>
       </c>
       <c r="E212" s="23" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F212" s="23">
         <v>2</v>
@@ -15223,9 +15285,11 @@
       <c r="L212" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M212" s="28"/>
+      <c r="M212" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N212" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O212" s="14" t="s">
         <v>139</v>
@@ -15235,7 +15299,7 @@
         <v>✅ OK</v>
       </c>
     </row>
-    <row r="213" spans="1:16" hidden="1">
+    <row r="213" spans="1:16">
       <c r="A213" s="23">
         <v>206</v>
       </c>
@@ -15300,7 +15364,7 @@
         <v>28</v>
       </c>
       <c r="E214" s="23" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F214" s="23">
         <v>2</v>
@@ -15320,7 +15384,7 @@
         <v>⚠️ Missing Key</v>
       </c>
       <c r="K214" s="23" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L214" s="23" t="s">
         <v>137</v>
@@ -15330,7 +15394,7 @@
         <v>34</v>
       </c>
       <c r="O214" s="14" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P214" s="14" t="str">
         <f t="shared" si="11"/>
@@ -15377,10 +15441,10 @@
         <v>137</v>
       </c>
       <c r="M215" s="28" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N215" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O215" s="14" t="s">
         <v>139</v>
@@ -15481,7 +15545,7 @@
         <v>137</v>
       </c>
       <c r="M217" s="28" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="N217" s="14" t="s">
         <v>35</v>
@@ -15534,7 +15598,7 @@
         <v>137</v>
       </c>
       <c r="M218" s="28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N218" s="14" t="s">
         <v>34</v>
@@ -15561,7 +15625,7 @@
         <v>28</v>
       </c>
       <c r="E219" s="23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F219" s="23">
         <v>2</v>
@@ -15588,7 +15652,7 @@
       </c>
       <c r="M219" s="28"/>
       <c r="N219" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O219" s="14" t="s">
         <v>139</v>
@@ -15612,7 +15676,7 @@
         <v>31</v>
       </c>
       <c r="E220" s="23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F220" s="23">
         <v>2</v>
@@ -15639,7 +15703,7 @@
       </c>
       <c r="M220" s="28"/>
       <c r="N220" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O220" s="14" t="s">
         <v>188</v>
@@ -15663,7 +15727,7 @@
         <v>31</v>
       </c>
       <c r="E221" s="23" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F221" s="23">
         <v>2</v>
@@ -15690,7 +15754,7 @@
       </c>
       <c r="M221" s="28"/>
       <c r="N221" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O221" s="14" t="s">
         <v>188</v>
@@ -15714,7 +15778,7 @@
         <v>31</v>
       </c>
       <c r="E222" s="23" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F222" s="23">
         <v>2</v>
@@ -15741,7 +15805,7 @@
       </c>
       <c r="M222" s="28"/>
       <c r="N222" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O222" s="14" t="s">
         <v>188</v>
@@ -15765,7 +15829,7 @@
         <v>31</v>
       </c>
       <c r="E223" s="23" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F223" s="23">
         <v>2</v>
@@ -15792,7 +15856,7 @@
       </c>
       <c r="M223" s="28"/>
       <c r="N223" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O223" s="14" t="s">
         <v>188</v>
@@ -15816,7 +15880,7 @@
         <v>31</v>
       </c>
       <c r="E224" s="23" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F224" s="23">
         <v>2</v>
@@ -15843,7 +15907,7 @@
       </c>
       <c r="M224" s="28"/>
       <c r="N224" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O224" s="14" t="s">
         <v>139</v>
@@ -15867,7 +15931,7 @@
         <v>31</v>
       </c>
       <c r="E225" s="23" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F225" s="23">
         <v>2</v>
@@ -15892,9 +15956,11 @@
       <c r="L225" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M225" s="28"/>
+      <c r="M225" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N225" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O225" s="14" t="s">
         <v>139</v>
@@ -15918,7 +15984,7 @@
         <v>31</v>
       </c>
       <c r="E226" s="23" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F226" s="23">
         <v>3</v>
@@ -15943,9 +16009,11 @@
       <c r="L226" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M226" s="28"/>
+      <c r="M226" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N226" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O226" s="14" t="s">
         <v>139</v>
@@ -15969,7 +16037,7 @@
         <v>31</v>
       </c>
       <c r="E227" s="23" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F227" s="23">
         <v>3</v>
@@ -15998,7 +16066,7 @@
         <v>177</v>
       </c>
       <c r="N227" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O227" s="14" t="s">
         <v>139</v>
@@ -16022,7 +16090,7 @@
         <v>31</v>
       </c>
       <c r="E228" s="23" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F228" s="23">
         <v>2</v>
@@ -16051,7 +16119,7 @@
         <v>177</v>
       </c>
       <c r="N228" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O228" s="14" t="s">
         <v>139</v>
@@ -16075,7 +16143,7 @@
         <v>31</v>
       </c>
       <c r="E229" s="23" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F229" s="23">
         <v>3</v>
@@ -16102,7 +16170,7 @@
       </c>
       <c r="M229" s="28"/>
       <c r="N229" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O229" s="14" t="s">
         <v>139</v>
@@ -16126,7 +16194,7 @@
         <v>31</v>
       </c>
       <c r="E230" s="23" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F230" s="23">
         <v>3</v>
@@ -16151,9 +16219,11 @@
       <c r="L230" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M230" s="28"/>
+      <c r="M230" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N230" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O230" s="14" t="s">
         <v>139</v>
@@ -16177,7 +16247,7 @@
         <v>31</v>
       </c>
       <c r="E231" s="23" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F231" s="23">
         <v>3</v>
@@ -16202,9 +16272,11 @@
       <c r="L231" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="M231" s="28"/>
+      <c r="M231" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N231" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O231" s="14" t="s">
         <v>139</v>
@@ -16228,7 +16300,7 @@
         <v>31</v>
       </c>
       <c r="E232" s="23" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F232" s="23">
         <v>3</v>
@@ -16255,7 +16327,7 @@
       </c>
       <c r="M232" s="28"/>
       <c r="N232" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O232" s="14" t="s">
         <v>139</v>
@@ -16279,7 +16351,7 @@
         <v>31</v>
       </c>
       <c r="E233" s="23" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F233" s="23">
         <v>2</v>
@@ -16306,7 +16378,7 @@
       </c>
       <c r="M233" s="28"/>
       <c r="N233" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O233" s="14" t="s">
         <v>139</v>
@@ -16330,7 +16402,7 @@
         <v>31</v>
       </c>
       <c r="E234" s="23" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F234" s="23">
         <v>3</v>
@@ -16357,7 +16429,7 @@
       </c>
       <c r="M234" s="28"/>
       <c r="N234" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O234" s="14" t="s">
         <v>139</v>
@@ -16381,7 +16453,7 @@
         <v>31</v>
       </c>
       <c r="E235" s="23" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F235" s="23">
         <v>2</v>
@@ -16408,7 +16480,7 @@
       </c>
       <c r="M235" s="28"/>
       <c r="N235" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O235" s="14" t="s">
         <v>139</v>
@@ -16432,7 +16504,7 @@
         <v>31</v>
       </c>
       <c r="E236" s="23" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F236" s="23">
         <v>2</v>
@@ -16459,7 +16531,7 @@
       </c>
       <c r="M236" s="28"/>
       <c r="N236" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O236" s="14" t="s">
         <v>139</v>
@@ -16476,14 +16548,14 @@
       <c r="B237" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="C237" s="26">
+      <c r="C237" s="24">
         <v>220</v>
       </c>
       <c r="D237" s="23" t="s">
         <v>31</v>
       </c>
       <c r="E237" s="23" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F237" s="23">
         <v>9</v>
@@ -16508,9 +16580,11 @@
       <c r="L237" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="M237" s="28"/>
+      <c r="M237" s="28" t="s">
+        <v>263</v>
+      </c>
       <c r="N237" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O237" s="14" t="s">
         <v>139</v>
@@ -16534,7 +16608,7 @@
         <v>31</v>
       </c>
       <c r="E238" s="23" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F238" s="23">
         <v>4</v>
@@ -16561,7 +16635,7 @@
       </c>
       <c r="M238" s="28"/>
       <c r="N238" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O238" s="14" t="s">
         <v>139</v>
@@ -16585,7 +16659,7 @@
         <v>28</v>
       </c>
       <c r="E239" s="23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F239" s="23">
         <v>2</v>
@@ -16608,14 +16682,14 @@
         <v>70</v>
       </c>
       <c r="L239" s="23" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M239" s="28"/>
       <c r="N239" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O239" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P239" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16636,7 +16710,7 @@
         <v>28</v>
       </c>
       <c r="E240" s="23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F240" s="23">
         <v>2</v>
@@ -16659,14 +16733,14 @@
         <v>70</v>
       </c>
       <c r="L240" s="23" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M240" s="28"/>
       <c r="N240" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O240" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P240" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16687,7 +16761,7 @@
         <v>28</v>
       </c>
       <c r="E241" s="23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F241" s="23">
         <v>2</v>
@@ -16710,14 +16784,14 @@
         <v>70</v>
       </c>
       <c r="L241" s="23" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M241" s="28"/>
       <c r="N241" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O241" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P241" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16738,7 +16812,7 @@
         <v>28</v>
       </c>
       <c r="E242" s="23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F242" s="23">
         <v>2</v>
@@ -16761,14 +16835,14 @@
         <v>70</v>
       </c>
       <c r="L242" s="23" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M242" s="28"/>
       <c r="N242" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O242" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P242" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16789,7 +16863,7 @@
         <v>28</v>
       </c>
       <c r="E243" s="23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F243" s="23">
         <v>2</v>
@@ -16812,14 +16886,14 @@
         <v>70</v>
       </c>
       <c r="L243" s="23" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M243" s="28"/>
       <c r="N243" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O243" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P243" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16840,7 +16914,7 @@
         <v>28</v>
       </c>
       <c r="E244" s="23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F244" s="23">
         <v>2</v>
@@ -16863,14 +16937,14 @@
         <v>70</v>
       </c>
       <c r="L244" s="23" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M244" s="28"/>
       <c r="N244" s="14" t="s">
         <v>34</v>
       </c>
       <c r="O244" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P244" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16920,10 +16994,10 @@
         <v>195</v>
       </c>
       <c r="N245" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O245" s="14" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P245" s="14" t="str">
         <f t="shared" si="11"/>
@@ -16973,10 +17047,10 @@
         <v>192</v>
       </c>
       <c r="N246" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O246" s="14" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P246" s="14" t="str">
         <f t="shared" si="11"/>
@@ -17026,10 +17100,10 @@
         <v>204</v>
       </c>
       <c r="N247" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O247" s="14" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P247" s="14" t="str">
         <f t="shared" si="11"/>
@@ -17050,7 +17124,7 @@
         <v>28</v>
       </c>
       <c r="E248" s="23" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F248" s="23">
         <v>2</v>
@@ -17076,13 +17150,13 @@
         <v>137</v>
       </c>
       <c r="M248" s="28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N248" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O248" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P248" s="14" t="str">
         <f t="shared" si="11"/>
@@ -17103,7 +17177,7 @@
         <v>28</v>
       </c>
       <c r="E249" s="23" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F249" s="23">
         <v>2</v>
@@ -17129,13 +17203,13 @@
         <v>137</v>
       </c>
       <c r="M249" s="28" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N249" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O249" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P249" s="14" t="str">
         <f t="shared" si="11"/>
@@ -17189,7 +17263,7 @@
         <v>27</v>
       </c>
       <c r="E251" s="23" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F251" s="23">
         <v>2</v>
@@ -17223,26 +17297,55 @@
       </c>
     </row>
     <row r="252" spans="1:16" hidden="1">
-      <c r="A252" s="23"/>
-      <c r="B252" s="23"/>
-      <c r="C252" s="24"/>
-      <c r="D252" s="23"/>
-      <c r="E252" s="23"/>
-      <c r="F252" s="23"/>
-      <c r="G252" s="23"/>
-      <c r="H252" s="23"/>
-      <c r="I252" s="23"/>
+      <c r="A252" s="23">
+        <v>241</v>
+      </c>
+      <c r="B252" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C252" s="24">
+        <v>5555</v>
+      </c>
+      <c r="D252" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E252" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="F252" s="23">
+        <v>2</v>
+      </c>
+      <c r="G252" s="23">
+        <v>2</v>
+      </c>
+      <c r="H252" s="23">
+        <v>0</v>
+      </c>
+      <c r="I252" s="23">
+        <f t="shared" ref="I252" si="12">MAX(0, F252-G252-H252)</f>
+        <v>0</v>
+      </c>
       <c r="J252" s="23" t="str">
-        <f t="shared" si="10"/>
-        <v>⚪ Unregistered</v>
-      </c>
-      <c r="K252" s="23"/>
-      <c r="L252" s="23"/>
-      <c r="M252" s="28"/>
-      <c r="N252" s="14"/>
-      <c r="O252" s="14"/>
+        <f t="shared" ref="J252" si="13">IF(I252&gt;0, "⚠️ Missing Key", IF(H252&gt;0, "🔑 Issued to Staff", IF(G252&gt;0, "🔒 In Custody", IF(F252=0, "⚪ Unregistered", "🔍 Under Audit"))))</f>
+        <v>🔒 In Custody</v>
+      </c>
+      <c r="K252" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="L252" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="M252" s="28" t="s">
+        <v>298</v>
+      </c>
+      <c r="N252" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="O252" s="14" t="s">
+        <v>321</v>
+      </c>
       <c r="P252" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="P252" si="14">IF(I252&gt;0, "🚨 REPLACE LOCK / KEY LOST", IF(ISNUMBER(SEARCH("Audit", O252)), "⚠️ AUDIT WITH EMPLOYEE", IF(ISNUMBER(SEARCH("Damaged", O252)), "⚠️ KEY DAMAGED / REPLACE", IF(ISNUMBER(SEARCH("Verification", O252)), "🔍 KEY VERIFICATION", IF(N252="Vacant", "🟢 AVAILABLE", "✅ OK")))))</f>
         <v>✅ OK</v>
       </c>
     </row>
@@ -17654,7 +17757,7 @@
     </row>
     <row r="4" spans="1:12" ht="24.95" customHeight="1">
       <c r="A4" s="40" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B4" s="69"/>
       <c r="C4" s="69"/>
@@ -17670,7 +17773,7 @@
     </row>
     <row r="5" spans="1:12" ht="18" customHeight="1">
       <c r="A5" s="54" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B5" s="69"/>
       <c r="C5" s="69"/>
@@ -17701,13 +17804,13 @@
         <v>124</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>88</v>
@@ -17716,10 +17819,10 @@
         <v>89</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -17742,10 +17845,10 @@
         <v>188</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I8" s="23" t="s">
         <v>108</v>
@@ -17754,10 +17857,10 @@
         <v>109</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -17780,10 +17883,10 @@
         <v>188</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H9" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I9" s="23" t="s">
         <v>108</v>
@@ -17792,10 +17895,10 @@
         <v>109</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -17818,10 +17921,10 @@
         <v>188</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I10" s="23" t="s">
         <v>108</v>
@@ -17830,10 +17933,10 @@
         <v>109</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -17856,10 +17959,10 @@
         <v>198</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I11" s="23" t="s">
         <v>94</v>
@@ -17868,10 +17971,10 @@
         <v>95</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -17894,10 +17997,10 @@
         <v>188</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>108</v>
@@ -17906,10 +18009,10 @@
         <v>109</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L12" s="23" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -17932,10 +18035,10 @@
         <v>201</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I13" s="23" t="s">
         <v>108</v>
@@ -17944,10 +18047,10 @@
         <v>109</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -17970,10 +18073,10 @@
         <v>188</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I14" s="23" t="s">
         <v>108</v>
@@ -17982,15 +18085,15 @@
         <v>109</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="23" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>49</v>
@@ -18008,10 +18111,10 @@
         <v>188</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I15" s="23" t="s">
         <v>108</v>
@@ -18020,15 +18123,15 @@
         <v>109</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="23" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>49</v>
@@ -18046,10 +18149,10 @@
         <v>188</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I16" s="23" t="s">
         <v>108</v>
@@ -18058,15 +18161,15 @@
         <v>109</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="23" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>59</v>
@@ -18084,10 +18187,10 @@
         <v>234</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I17" s="23" t="s">
         <v>108</v>
@@ -18096,15 +18199,15 @@
         <v>109</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="23" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B18" s="23" t="s">
         <v>63</v>
@@ -18122,10 +18225,10 @@
         <v>237</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I18" s="23" t="s">
         <v>108</v>
@@ -18134,15 +18237,15 @@
         <v>109</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="23" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B19" s="23" t="s">
         <v>63</v>
@@ -18160,10 +18263,10 @@
         <v>237</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I19" s="23" t="s">
         <v>108</v>
@@ -18172,15 +18275,15 @@
         <v>109</v>
       </c>
       <c r="K19" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="23" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B20" s="23" t="s">
         <v>43</v>
@@ -18195,13 +18298,13 @@
         <v>103</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I20" s="23" t="s">
         <v>94</v>
@@ -18210,15 +18313,15 @@
         <v>95</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="23" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>54</v>
@@ -18230,16 +18333,16 @@
         <v>31</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F21" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I21" s="23" t="s">
         <v>108</v>
@@ -18248,15 +18351,15 @@
         <v>109</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="23" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B22" s="23" t="s">
         <v>45</v>
@@ -18268,16 +18371,16 @@
         <v>31</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F22" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I22" s="23" t="s">
         <v>108</v>
@@ -18286,15 +18389,15 @@
         <v>109</v>
       </c>
       <c r="K22" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="23" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B23" s="23" t="s">
         <v>54</v>
@@ -18306,16 +18409,16 @@
         <v>31</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F23" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I23" s="23" t="s">
         <v>108</v>
@@ -18324,15 +18427,15 @@
         <v>109</v>
       </c>
       <c r="K23" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="23" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B24" s="23" t="s">
         <v>54</v>
@@ -18344,16 +18447,16 @@
         <v>31</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F24" s="27" t="s">
         <v>188</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I24" s="23" t="s">
         <v>108</v>
@@ -18362,15 +18465,15 @@
         <v>109</v>
       </c>
       <c r="K24" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L24" s="23" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="29.1" customHeight="1">
       <c r="A25" s="23" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B25" s="23" t="s">
         <v>45</v>
@@ -18385,13 +18488,13 @@
         <v>92</v>
       </c>
       <c r="F25" s="27" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I25" s="23" t="s">
         <v>94</v>
@@ -18400,15 +18503,15 @@
         <v>95</v>
       </c>
       <c r="K25" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="29.1" customHeight="1">
       <c r="A26" s="23" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>45</v>
@@ -18423,13 +18526,13 @@
         <v>92</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I26" s="23" t="s">
         <v>94</v>
@@ -18438,15 +18541,15 @@
         <v>95</v>
       </c>
       <c r="K26" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="29.1" customHeight="1">
       <c r="A27" s="23" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B27" s="23" t="s">
         <v>47</v>
@@ -18461,13 +18564,13 @@
         <v>100</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I27" s="23" t="s">
         <v>94</v>
@@ -18476,10 +18579,10 @@
         <v>95</v>
       </c>
       <c r="K27" s="23" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -18563,7 +18666,7 @@
     </row>
     <row r="4" spans="2:14" ht="24.95" customHeight="1">
       <c r="B4" s="40" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C4" s="69"/>
       <c r="D4" s="69"/>
@@ -18580,7 +18683,7 @@
     </row>
     <row r="5" spans="2:14" ht="18" customHeight="1">
       <c r="B5" s="54" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C5" s="69"/>
       <c r="D5" s="69"/>
@@ -18597,7 +18700,7 @@
     </row>
     <row r="7" spans="2:14" ht="21.95" customHeight="1">
       <c r="B7" s="62" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C7" s="70"/>
       <c r="D7" s="70"/>
@@ -18614,25 +18717,25 @@
     </row>
     <row r="8" spans="2:14" ht="24" customHeight="1">
       <c r="B8" s="16" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>26</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>34</v>
@@ -18641,10 +18744,10 @@
         <v>35</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>127</v>
@@ -18765,7 +18868,7 @@
       </c>
       <c r="C11" s="18">
         <f>COUNTIF(Table_Tracker[Zone], B11)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="18">
         <f>COUNTIFS(Table_Tracker[Zone], B11, Table_Tracker[Lock Type], "Planter")</f>
@@ -18773,7 +18876,7 @@
       </c>
       <c r="E11" s="18">
         <f>COUNTIFS(Table_Tracker[Zone], B11, Table_Tracker[Lock Type], "Cupboard")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="18">
         <f>COUNTIFS(Table_Tracker[Zone], B11, Table_Tracker[Lock Type], "Locker")</f>
@@ -18797,11 +18900,11 @@
       </c>
       <c r="K11" s="18">
         <f>COUNTIFS(Table_Tracker[Zone], B11, Table_Tracker[Lock Status], "Common Asset")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L11" s="18">
         <f>SUMIFS(Table_Tracker[Spare Keys (BMS)], Table_Tracker[Zone], B11)</f>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M11" s="18">
         <f>SUMIFS(Table_Tracker[Issued Keys], Table_Tracker[Zone], B11)</f>
@@ -18960,7 +19063,7 @@
       </c>
       <c r="L14" s="18">
         <f>SUMIFS(Table_Tracker[Spare Keys (BMS)], Table_Tracker[Zone], B14)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M14" s="18">
         <f>SUMIFS(Table_Tracker[Issued Keys], Table_Tracker[Zone], B14)</f>
@@ -18968,7 +19071,7 @@
       </c>
       <c r="N14" s="18">
         <f>SUMIFS(Table_Tracker[Missing Keys], Table_Tracker[Zone], B14)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="18" customHeight="1">
@@ -19225,7 +19328,7 @@
       </c>
       <c r="L19" s="18">
         <f>SUMIFS(Table_Tracker[Spare Keys (BMS)], Table_Tracker[Zone], B19)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M19" s="18">
         <f>SUMIFS(Table_Tracker[Issued Keys], Table_Tracker[Zone], B19)</f>
@@ -19233,7 +19336,7 @@
       </c>
       <c r="N19" s="18">
         <f>SUMIFS(Table_Tracker[Missing Keys], Table_Tracker[Zone], B19)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="2:14" ht="18" customHeight="1">
@@ -19397,11 +19500,11 @@
     </row>
     <row r="23" spans="2:14" ht="20.100000000000001" customHeight="1">
       <c r="B23" s="19" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C23" s="20">
         <f t="shared" ref="C23:N23" si="0">SUM(C9:C22)</f>
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D23" s="20">
         <f t="shared" si="0"/>
@@ -19409,7 +19512,7 @@
       </c>
       <c r="E23" s="20">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F23" s="20">
         <f t="shared" si="0"/>
@@ -19433,11 +19536,11 @@
       </c>
       <c r="K23" s="20">
         <f t="shared" si="0"/>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L23" s="20">
         <f t="shared" si="0"/>
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="M23" s="20">
         <f t="shared" si="0"/>
@@ -19445,7 +19548,7 @@
       </c>
       <c r="N23" s="20">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -19511,7 +19614,7 @@
     </row>
     <row r="4" spans="1:11" ht="24.95" customHeight="1">
       <c r="A4" s="40" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B4" s="69"/>
       <c r="C4" s="69"/>
@@ -19526,27 +19629,27 @@
     </row>
     <row r="5" spans="1:11" ht="15.95" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H5" s="15"/>
       <c r="I5" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J5" s="15"/>
       <c r="K5" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.95" customHeight="1">
@@ -19571,7 +19674,7 @@
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.95" customHeight="1">
@@ -19596,7 +19699,7 @@
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.95" customHeight="1">
@@ -19609,19 +19712,19 @@
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.95" customHeight="1">
@@ -19655,7 +19758,7 @@
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
